--- a/m3.xlsx
+++ b/m3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\سعيات\م2 - ف2\steam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E4A072-9D18-41D6-B163-0BAD36CDC8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133F9B08-C594-4B16-9114-7807A8D4D80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -354,9 +354,6 @@
     <t>يسر حسين محسن ناصر</t>
   </si>
   <si>
-    <t>يقين كاظم تركي المالكي</t>
-  </si>
-  <si>
     <t>نبائط اشباه الموصلات</t>
   </si>
   <si>
@@ -370,6 +367,9 @@
   </si>
   <si>
     <t>التحليلات الهندسية II</t>
+  </si>
+  <si>
+    <t>يقين كاظم تركي عذيب</t>
   </si>
 </sst>
 </file>
@@ -493,17 +493,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -807,42 +807,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="9"/>
+      <c r="I1" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="10"/>
-      <c r="I1" s="11" t="s">
+      <c r="J1" s="8"/>
+      <c r="K1" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="8"/>
+      <c r="M1" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
     </row>
     <row r="2" spans="1:16" ht="21" x14ac:dyDescent="0.3">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>3102</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C104" s="6">
         <v>38</v>
@@ -3560,7 +3560,6 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="M1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="C1:D1"/>
@@ -3569,6 +3568,7 @@
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/m3.xlsx
+++ b/m3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\سعيات\م2 - ف2\steam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133F9B08-C594-4B16-9114-7807A8D4D80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C5762C-C3AA-4150-963A-D846E96295EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -147,9 +147,6 @@
     <t>رسول رحيم دحام عناد</t>
   </si>
   <si>
-    <t>رقيه محسن جبير ناصر البو شيخ عبدالله</t>
-  </si>
-  <si>
     <t>روتاج رعد حسين مفتي</t>
   </si>
   <si>
@@ -370,6 +367,9 @@
   </si>
   <si>
     <t>يقين كاظم تركي عذيب</t>
+  </si>
+  <si>
+    <t>رقيه محسن جبير ناصر</t>
   </si>
 </sst>
 </file>
@@ -818,23 +818,23 @@
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F1" s="9"/>
       <c r="G1" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H1" s="9"/>
       <c r="I1" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J1" s="8"/>
       <c r="K1" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L1" s="8"/>
       <c r="M1" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N1" s="8"/>
       <c r="O1" s="8"/>
@@ -1655,7 +1655,7 @@
         <v>3033</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="C35" s="6">
         <v>38</v>
@@ -1679,7 +1679,7 @@
         <v>3034</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C36" s="6">
         <v>38</v>
@@ -1703,7 +1703,7 @@
         <v>3035</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C37" s="6">
         <v>38</v>
@@ -1727,7 +1727,7 @@
         <v>3036</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C38" s="6">
         <v>29</v>
@@ -1751,7 +1751,7 @@
         <v>3037</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C39" s="6">
         <v>38</v>
@@ -1775,7 +1775,7 @@
         <v>3038</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40" s="6">
         <v>32</v>
@@ -1799,7 +1799,7 @@
         <v>3039</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C41" s="6">
         <v>32</v>
@@ -1823,7 +1823,7 @@
         <v>3040</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C42" s="6">
         <v>32</v>
@@ -1847,7 +1847,7 @@
         <v>3041</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C43" s="6">
         <v>26</v>
@@ -1871,7 +1871,7 @@
         <v>3042</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C44" s="6">
         <v>38</v>
@@ -1895,7 +1895,7 @@
         <v>3043</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C45" s="6">
         <v>32</v>
@@ -1919,7 +1919,7 @@
         <v>3044</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C46" s="6">
         <v>38</v>
@@ -1943,7 +1943,7 @@
         <v>3045</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C47" s="6">
         <v>32</v>
@@ -1967,7 +1967,7 @@
         <v>3046</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C48" s="6">
         <v>14</v>
@@ -1991,7 +1991,7 @@
         <v>3047</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C49" s="6">
         <v>29</v>
@@ -2015,7 +2015,7 @@
         <v>3048</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C50" s="6">
         <v>29</v>
@@ -2039,7 +2039,7 @@
         <v>3049</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C51" s="6">
         <v>23</v>
@@ -2063,7 +2063,7 @@
         <v>3050</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C52" s="6">
         <v>29</v>
@@ -2087,7 +2087,7 @@
         <v>3051</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C53" s="6">
         <v>32</v>
@@ -2111,7 +2111,7 @@
         <v>3052</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C54" s="6">
         <v>32</v>
@@ -2135,7 +2135,7 @@
         <v>3053</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C55" s="6">
         <v>26</v>
@@ -2159,7 +2159,7 @@
         <v>3054</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C56" s="6">
         <v>35</v>
@@ -2183,7 +2183,7 @@
         <v>3055</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C57" s="6">
         <v>38</v>
@@ -2207,7 +2207,7 @@
         <v>3056</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C58" s="6">
         <v>38</v>
@@ -2231,7 +2231,7 @@
         <v>3057</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C59" s="6">
         <v>32</v>
@@ -2255,7 +2255,7 @@
         <v>3058</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C60" s="6">
         <v>32</v>
@@ -2279,7 +2279,7 @@
         <v>3059</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C61" s="6">
         <v>32</v>
@@ -2303,7 +2303,7 @@
         <v>3060</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C62" s="6">
         <v>23</v>
@@ -2327,7 +2327,7 @@
         <v>3061</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C63" s="6">
         <v>35</v>
@@ -2351,7 +2351,7 @@
         <v>3062</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C64" s="6">
         <v>29</v>
@@ -2375,7 +2375,7 @@
         <v>3063</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C65" s="6">
         <v>38</v>
@@ -2399,7 +2399,7 @@
         <v>3064</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C66" s="6">
         <v>35</v>
@@ -2423,7 +2423,7 @@
         <v>3065</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C67" s="6">
         <v>32</v>
@@ -2447,7 +2447,7 @@
         <v>3066</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C68" s="6">
         <v>38</v>
@@ -2471,7 +2471,7 @@
         <v>3067</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C69" s="6">
         <v>32</v>
@@ -2495,7 +2495,7 @@
         <v>3068</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C70" s="6">
         <v>38</v>
@@ -2519,7 +2519,7 @@
         <v>3069</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C71" s="6">
         <v>26</v>
@@ -2543,7 +2543,7 @@
         <v>3070</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C72" s="6">
         <v>32</v>
@@ -2567,7 +2567,7 @@
         <v>3071</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C73" s="6">
         <v>35</v>
@@ -2591,7 +2591,7 @@
         <v>3072</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C74" s="6">
         <v>0</v>
@@ -2615,7 +2615,7 @@
         <v>3073</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C75" s="6">
         <v>32</v>
@@ -2639,7 +2639,7 @@
         <v>3074</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C76" s="6">
         <v>14</v>
@@ -2663,7 +2663,7 @@
         <v>3075</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C77" s="6">
         <v>35</v>
@@ -2687,7 +2687,7 @@
         <v>3076</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C78" s="6">
         <v>29</v>
@@ -2711,7 +2711,7 @@
         <v>3077</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C79" s="6">
         <v>23</v>
@@ -2735,7 +2735,7 @@
         <v>3078</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C80" s="6">
         <v>14</v>
@@ -2759,7 +2759,7 @@
         <v>3079</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C81" s="6">
         <v>26</v>
@@ -2783,7 +2783,7 @@
         <v>3080</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C82" s="6">
         <v>26</v>
@@ -2807,7 +2807,7 @@
         <v>3081</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C83" s="6">
         <v>32</v>
@@ -2831,7 +2831,7 @@
         <v>3082</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C84" s="6">
         <v>14</v>
@@ -2855,7 +2855,7 @@
         <v>3083</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C85" s="6">
         <v>32</v>
@@ -2879,7 +2879,7 @@
         <v>3084</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C86" s="6">
         <v>32</v>
@@ -2903,7 +2903,7 @@
         <v>3085</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C87" s="6">
         <v>29</v>
@@ -2927,7 +2927,7 @@
         <v>3086</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C88" s="6">
         <v>23</v>
@@ -2951,7 +2951,7 @@
         <v>3087</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C89" s="6">
         <v>26</v>
@@ -2975,7 +2975,7 @@
         <v>3088</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C90" s="6">
         <v>26</v>
@@ -2999,7 +2999,7 @@
         <v>3089</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C91" s="6">
         <v>32</v>
@@ -3023,7 +3023,7 @@
         <v>3090</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C92" s="6">
         <v>23</v>
@@ -3047,7 +3047,7 @@
         <v>3091</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C93" s="6">
         <v>23</v>
@@ -3071,7 +3071,7 @@
         <v>3092</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C94" s="6">
         <v>14</v>
@@ -3095,7 +3095,7 @@
         <v>3093</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C95" s="6">
         <v>29</v>
@@ -3119,7 +3119,7 @@
         <v>3094</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C96" s="6">
         <v>32</v>
@@ -3143,7 +3143,7 @@
         <v>3095</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C97" s="6">
         <v>32</v>
@@ -3167,7 +3167,7 @@
         <v>3096</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C98" s="6">
         <v>29</v>
@@ -3191,7 +3191,7 @@
         <v>3097</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C99" s="6">
         <v>32</v>
@@ -3215,7 +3215,7 @@
         <v>3098</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C100" s="6">
         <v>29</v>
@@ -3239,7 +3239,7 @@
         <v>3099</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C101" s="6">
         <v>35</v>
@@ -3263,7 +3263,7 @@
         <v>3100</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C102" s="6">
         <v>29</v>
@@ -3287,7 +3287,7 @@
         <v>3101</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C103" s="6">
         <v>38</v>
@@ -3311,7 +3311,7 @@
         <v>3102</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C104" s="6">
         <v>38</v>

--- a/m3.xlsx
+++ b/m3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\سعيات\م2 - ف2\steam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F9BDF1-3549-46F3-8501-0B04626E76CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A579449-124C-4C7A-89F4-5709A6B2DD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -461,12 +461,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -476,14 +470,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -787,3572 +787,3980 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9" t="s">
+      <c r="D1" s="8"/>
+      <c r="E1" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9" t="s">
+      <c r="F1" s="8"/>
+      <c r="G1" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9" t="s">
+      <c r="H1" s="8"/>
+      <c r="I1" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9" t="s">
+      <c r="J1" s="8"/>
+      <c r="K1" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9" t="s">
+      <c r="L1" s="8"/>
+      <c r="M1" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="N1" s="9"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
     </row>
     <row r="2" spans="1:16" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A3" s="5">
+      <c r="A3" s="3">
         <v>3001</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="3">
         <v>14</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="3">
         <v>0</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <v>23</v>
       </c>
-      <c r="F3" s="6">
-        <v>8</v>
-      </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6">
+      <c r="F3" s="4">
+        <v>8</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4">
+        <v>35</v>
+      </c>
+      <c r="J3" s="4">
+        <v>10</v>
+      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4">
         <v>24</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A4" s="5">
+      <c r="A4" s="3">
         <v>3002</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3">
         <v>14</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <v>0</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>29</v>
       </c>
-      <c r="F4" s="6">
-        <v>7</v>
-      </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6">
+      <c r="F4" s="4">
+        <v>7</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4">
+        <v>33</v>
+      </c>
+      <c r="J4" s="4">
+        <v>10</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4">
         <v>23</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A5" s="5">
+      <c r="A5" s="3">
         <v>3003</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3">
         <v>14</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <v>0</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>20</v>
       </c>
-      <c r="F5" s="6">
-        <v>6</v>
-      </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6">
+      <c r="F5" s="4">
+        <v>6</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4">
+        <v>26</v>
+      </c>
+      <c r="J5" s="4">
+        <v>10</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4">
         <v>9</v>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A6" s="5">
+      <c r="A6" s="3">
         <v>3004</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="5">
-        <v>32</v>
-      </c>
-      <c r="D6" s="5">
-        <v>8</v>
-      </c>
-      <c r="E6" s="6">
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3">
+        <v>32</v>
+      </c>
+      <c r="D6" s="3">
+        <v>8</v>
+      </c>
+      <c r="E6" s="4">
         <v>29</v>
       </c>
-      <c r="F6" s="6">
-        <v>6</v>
-      </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6">
+      <c r="F6" s="4">
+        <v>6</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4">
+        <v>27</v>
+      </c>
+      <c r="J6" s="4">
+        <v>9</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4">
         <v>24</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A7" s="5">
+      <c r="A7" s="3">
         <v>3005</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>32</v>
-      </c>
-      <c r="D7" s="5">
-        <v>8</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="C7" s="3">
+        <v>32</v>
+      </c>
+      <c r="D7" s="3">
+        <v>8</v>
+      </c>
+      <c r="E7" s="4">
         <v>27</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="4">
         <v>4</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6">
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4">
+        <v>30</v>
+      </c>
+      <c r="J7" s="4">
+        <v>7</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4">
         <v>26</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A8" s="5">
+      <c r="A8" s="3">
         <v>3006</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3">
         <v>38</v>
       </c>
-      <c r="D8" s="5">
-        <v>10</v>
-      </c>
-      <c r="E8" s="6">
+      <c r="D8" s="3">
+        <v>10</v>
+      </c>
+      <c r="E8" s="4">
         <v>40</v>
       </c>
-      <c r="F8" s="6">
-        <v>10</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6">
+      <c r="F8" s="4">
+        <v>10</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4">
         <v>40</v>
       </c>
-      <c r="N8" s="6">
+      <c r="J8" s="4">
+        <v>10</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4">
+        <v>40</v>
+      </c>
+      <c r="N8" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A9" s="5">
+      <c r="A9" s="3">
         <v>3007</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="3">
         <v>26</v>
       </c>
-      <c r="D9" s="5">
-        <v>6</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="D9" s="3">
+        <v>6</v>
+      </c>
+      <c r="E9" s="4">
         <v>25</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="4">
         <v>4</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6">
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4">
+        <v>29</v>
+      </c>
+      <c r="J9" s="4">
+        <v>9</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4">
         <v>28</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A10" s="5">
+      <c r="A10" s="3">
         <v>3008</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="5">
-        <v>32</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="3">
+        <v>32</v>
+      </c>
+      <c r="D10" s="3">
         <v>4</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="4">
         <v>22</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="4">
         <v>5</v>
       </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6">
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4">
+        <v>28</v>
+      </c>
+      <c r="J10" s="4">
+        <v>10</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4">
         <v>25</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A11" s="5">
+      <c r="A11" s="3">
         <v>3009</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="5">
-        <v>32</v>
-      </c>
-      <c r="D11" s="5">
-        <v>8</v>
-      </c>
-      <c r="E11" s="6">
+      <c r="C11" s="3">
+        <v>32</v>
+      </c>
+      <c r="D11" s="3">
+        <v>8</v>
+      </c>
+      <c r="E11" s="4">
         <v>23</v>
       </c>
-      <c r="F11" s="6">
-        <v>8</v>
-      </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6">
+      <c r="F11" s="4">
+        <v>8</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4">
+        <v>36</v>
+      </c>
+      <c r="J11" s="4">
+        <v>10</v>
+      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4">
         <v>27</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A12" s="5">
+      <c r="A12" s="3">
         <v>3010</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="3">
         <v>38</v>
       </c>
-      <c r="D12" s="5">
-        <v>10</v>
-      </c>
-      <c r="E12" s="6">
+      <c r="D12" s="3">
+        <v>10</v>
+      </c>
+      <c r="E12" s="4">
         <v>40</v>
       </c>
-      <c r="F12" s="6">
-        <v>10</v>
-      </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6">
+      <c r="F12" s="4">
+        <v>10</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4">
         <v>40</v>
       </c>
-      <c r="N12" s="6">
+      <c r="J12" s="4">
+        <v>10</v>
+      </c>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4">
+        <v>40</v>
+      </c>
+      <c r="N12" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A13" s="5">
+      <c r="A13" s="3">
         <v>3011</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="3">
         <v>35</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="3">
         <v>9</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="4">
         <v>37</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="4">
         <v>9</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6">
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4">
+        <v>38</v>
+      </c>
+      <c r="J13" s="4">
+        <v>10</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4">
         <v>40</v>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A14" s="5">
+      <c r="A14" s="3">
         <v>3012</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="3">
         <v>38</v>
       </c>
-      <c r="D14" s="5">
-        <v>10</v>
-      </c>
-      <c r="E14" s="6">
-        <v>32</v>
-      </c>
-      <c r="F14" s="6">
+      <c r="D14" s="3">
+        <v>10</v>
+      </c>
+      <c r="E14" s="4">
+        <v>32</v>
+      </c>
+      <c r="F14" s="4">
         <v>4</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6">
-        <v>32</v>
-      </c>
-      <c r="N14" s="6">
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4">
+        <v>40</v>
+      </c>
+      <c r="J14" s="4">
+        <v>10</v>
+      </c>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4">
+        <v>32</v>
+      </c>
+      <c r="N14" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A15" s="5">
+      <c r="A15" s="3">
         <v>3013</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="3">
         <v>23</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="3">
         <v>5</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="4">
         <v>21</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="4">
         <v>0</v>
       </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6">
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4">
+        <v>31</v>
+      </c>
+      <c r="J15" s="4">
+        <v>10</v>
+      </c>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4">
         <v>21</v>
       </c>
-      <c r="N15" s="6">
+      <c r="N15" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A16" s="5">
+      <c r="A16" s="3">
         <v>3014</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="5">
-        <v>32</v>
-      </c>
-      <c r="D16" s="5">
-        <v>8</v>
-      </c>
-      <c r="E16" s="6">
+      <c r="C16" s="3">
+        <v>32</v>
+      </c>
+      <c r="D16" s="3">
+        <v>8</v>
+      </c>
+      <c r="E16" s="4">
         <v>27</v>
       </c>
-      <c r="F16" s="6">
-        <v>7</v>
-      </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6">
+      <c r="F16" s="4">
+        <v>7</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4">
+        <v>37</v>
+      </c>
+      <c r="J16" s="4">
+        <v>9</v>
+      </c>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4">
         <v>25</v>
       </c>
-      <c r="N16" s="6">
+      <c r="N16" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A17" s="5">
+      <c r="A17" s="3">
         <v>3015</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="3">
         <v>35</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="3">
         <v>9</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="4">
         <v>28</v>
       </c>
-      <c r="F17" s="6">
-        <v>8</v>
-      </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6">
+      <c r="F17" s="4">
+        <v>8</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4">
+        <v>32</v>
+      </c>
+      <c r="J17" s="4">
+        <v>10</v>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4">
         <v>30</v>
       </c>
-      <c r="N17" s="6">
+      <c r="N17" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A18" s="5">
+      <c r="A18" s="3">
         <v>3016</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="5">
-        <v>32</v>
-      </c>
-      <c r="D18" s="5">
-        <v>8</v>
-      </c>
-      <c r="E18" s="6">
+      <c r="C18" s="3">
+        <v>32</v>
+      </c>
+      <c r="D18" s="3">
+        <v>8</v>
+      </c>
+      <c r="E18" s="4">
         <v>18</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="4">
         <v>5</v>
       </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6">
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4">
+        <v>29</v>
+      </c>
+      <c r="J18" s="4">
+        <v>2</v>
+      </c>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4">
         <v>26</v>
       </c>
-      <c r="N18" s="6">
+      <c r="N18" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A19" s="5">
+      <c r="A19" s="3">
         <v>3017</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="5">
-        <v>32</v>
-      </c>
-      <c r="D19" s="5">
-        <v>8</v>
-      </c>
-      <c r="E19" s="6">
+      <c r="C19" s="3">
+        <v>32</v>
+      </c>
+      <c r="D19" s="3">
+        <v>8</v>
+      </c>
+      <c r="E19" s="4">
         <v>30</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="4">
         <v>4</v>
       </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6">
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4">
+        <v>32</v>
+      </c>
+      <c r="J19" s="4">
+        <v>8</v>
+      </c>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4">
         <v>29</v>
       </c>
-      <c r="N19" s="6">
+      <c r="N19" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A20" s="5">
+      <c r="A20" s="3">
         <v>3018</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="3">
         <v>29</v>
       </c>
-      <c r="D20" s="5">
-        <v>7</v>
-      </c>
-      <c r="E20" s="6">
+      <c r="D20" s="3">
+        <v>7</v>
+      </c>
+      <c r="E20" s="4">
         <v>29</v>
       </c>
-      <c r="F20" s="6">
-        <v>7</v>
-      </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6">
-        <v>32</v>
-      </c>
-      <c r="N20" s="6">
+      <c r="F20" s="4">
+        <v>7</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4">
+        <v>34</v>
+      </c>
+      <c r="J20" s="4">
+        <v>9</v>
+      </c>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4">
+        <v>32</v>
+      </c>
+      <c r="N20" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A21" s="5">
+      <c r="A21" s="3">
         <v>3019</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="3">
         <v>35</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="3">
         <v>9</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="4">
         <v>23</v>
       </c>
-      <c r="F21" s="6">
-        <v>6</v>
-      </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6">
+      <c r="F21" s="4">
+        <v>6</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4">
+        <v>33</v>
+      </c>
+      <c r="J21" s="4">
+        <v>9</v>
+      </c>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4">
         <v>25</v>
       </c>
-      <c r="N21" s="6">
+      <c r="N21" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A22" s="5">
+      <c r="A22" s="3">
         <v>3020</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="3">
         <v>23</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="3">
         <v>3</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="4">
         <v>25</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="4">
         <v>5</v>
       </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6">
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4">
+        <v>32</v>
+      </c>
+      <c r="J22" s="4">
+        <v>8</v>
+      </c>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4">
         <v>25</v>
       </c>
-      <c r="N22" s="6">
+      <c r="N22" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A23" s="5">
+      <c r="A23" s="3">
         <v>3021</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="3">
         <v>26</v>
       </c>
-      <c r="D23" s="5">
-        <v>6</v>
-      </c>
-      <c r="E23" s="6">
+      <c r="D23" s="3">
+        <v>6</v>
+      </c>
+      <c r="E23" s="4">
         <v>21</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="4">
         <v>4</v>
       </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6">
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4">
+        <v>32</v>
+      </c>
+      <c r="J23" s="4">
+        <v>8</v>
+      </c>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4">
         <v>28</v>
       </c>
-      <c r="N23" s="6">
+      <c r="N23" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A24" s="5">
+      <c r="A24" s="3">
         <v>3022</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="5">
-        <v>32</v>
-      </c>
-      <c r="D24" s="5">
-        <v>8</v>
-      </c>
-      <c r="E24" s="6">
+      <c r="C24" s="3">
+        <v>32</v>
+      </c>
+      <c r="D24" s="3">
+        <v>8</v>
+      </c>
+      <c r="E24" s="4">
         <v>29</v>
       </c>
-      <c r="F24" s="6">
-        <v>8</v>
-      </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6">
+      <c r="F24" s="4">
+        <v>8</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4">
+        <v>31</v>
+      </c>
+      <c r="J24" s="4">
+        <v>10</v>
+      </c>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4">
         <v>26</v>
       </c>
-      <c r="N24" s="6">
+      <c r="N24" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A25" s="5">
+      <c r="A25" s="3">
         <v>3023</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="3">
         <v>23</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="3">
         <v>4</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="4">
         <v>23</v>
       </c>
-      <c r="F25" s="6">
-        <v>6</v>
-      </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6">
+      <c r="F25" s="4">
+        <v>6</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4">
+        <v>35</v>
+      </c>
+      <c r="J25" s="4">
+        <v>7</v>
+      </c>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4">
         <v>25</v>
       </c>
-      <c r="N25" s="6">
+      <c r="N25" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A26" s="5">
+      <c r="A26" s="3">
         <v>3024</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="5">
-        <v>32</v>
-      </c>
-      <c r="D26" s="5">
-        <v>8</v>
-      </c>
-      <c r="E26" s="6">
-        <v>32</v>
-      </c>
-      <c r="F26" s="6">
+      <c r="C26" s="3">
+        <v>32</v>
+      </c>
+      <c r="D26" s="3">
+        <v>8</v>
+      </c>
+      <c r="E26" s="4">
+        <v>32</v>
+      </c>
+      <c r="F26" s="4">
         <v>9</v>
       </c>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6">
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4">
         <v>40</v>
       </c>
-      <c r="N26" s="6">
+      <c r="J26" s="4">
+        <v>9</v>
+      </c>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4">
+        <v>40</v>
+      </c>
+      <c r="N26" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A27" s="5">
+      <c r="A27" s="3">
         <v>3025</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="5">
-        <v>32</v>
-      </c>
-      <c r="D27" s="5">
-        <v>8</v>
-      </c>
-      <c r="E27" s="6">
+      <c r="C27" s="3">
+        <v>32</v>
+      </c>
+      <c r="D27" s="3">
+        <v>8</v>
+      </c>
+      <c r="E27" s="4">
         <v>18</v>
       </c>
-      <c r="F27" s="6">
-        <v>6</v>
-      </c>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6">
+      <c r="F27" s="4">
+        <v>6</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4">
+        <v>27</v>
+      </c>
+      <c r="J27" s="4">
+        <v>6</v>
+      </c>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4">
         <v>24</v>
       </c>
-      <c r="N27" s="6">
+      <c r="N27" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A28" s="5">
+      <c r="A28" s="3">
         <v>3026</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="5">
-        <v>32</v>
-      </c>
-      <c r="D28" s="5">
-        <v>8</v>
-      </c>
-      <c r="E28" s="6">
+      <c r="C28" s="3">
+        <v>32</v>
+      </c>
+      <c r="D28" s="3">
+        <v>8</v>
+      </c>
+      <c r="E28" s="4">
         <v>31</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="4">
         <v>5</v>
       </c>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6">
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4">
+        <v>34</v>
+      </c>
+      <c r="J28" s="4">
+        <v>9</v>
+      </c>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4">
         <v>27</v>
       </c>
-      <c r="N28" s="6">
+      <c r="N28" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A29" s="5">
+      <c r="A29" s="3">
         <v>3027</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="3">
         <v>35</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="3">
         <v>9</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="4">
         <v>31</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="4">
         <v>3</v>
       </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6">
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4">
+        <v>30</v>
+      </c>
+      <c r="J29" s="4">
+        <v>10</v>
+      </c>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4">
         <v>26</v>
       </c>
-      <c r="N29" s="6">
+      <c r="N29" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A30" s="5">
+      <c r="A30" s="3">
         <v>3028</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="5">
+      <c r="B30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="3">
         <v>38</v>
       </c>
-      <c r="D30" s="5">
-        <v>10</v>
-      </c>
-      <c r="E30" s="6">
+      <c r="D30" s="3">
+        <v>10</v>
+      </c>
+      <c r="E30" s="4">
         <v>24</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="4">
         <v>5</v>
       </c>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6">
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4">
+        <v>34</v>
+      </c>
+      <c r="J30" s="4">
+        <v>8</v>
+      </c>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4">
         <v>25</v>
       </c>
-      <c r="N30" s="6">
+      <c r="N30" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A31" s="5">
+      <c r="A31" s="3">
         <v>3029</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="3">
         <v>26</v>
       </c>
-      <c r="D31" s="5">
-        <v>6</v>
-      </c>
-      <c r="E31" s="6">
+      <c r="D31" s="3">
+        <v>6</v>
+      </c>
+      <c r="E31" s="4">
         <v>35</v>
       </c>
-      <c r="F31" s="6">
-        <v>6</v>
-      </c>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6">
-        <v>32</v>
-      </c>
-      <c r="N31" s="6">
+      <c r="F31" s="4">
+        <v>6</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4">
+        <v>36</v>
+      </c>
+      <c r="J31" s="4">
+        <v>10</v>
+      </c>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4">
+        <v>32</v>
+      </c>
+      <c r="N31" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A32" s="5">
+      <c r="A32" s="3">
         <v>3030</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C32" s="5">
-        <v>32</v>
-      </c>
-      <c r="D32" s="5">
-        <v>10</v>
-      </c>
-      <c r="E32" s="6">
+      <c r="C32" s="3">
+        <v>32</v>
+      </c>
+      <c r="D32" s="3">
+        <v>10</v>
+      </c>
+      <c r="E32" s="4">
         <v>36</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="4">
         <v>9</v>
       </c>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6">
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4">
+        <v>38</v>
+      </c>
+      <c r="J32" s="4">
+        <v>10</v>
+      </c>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4">
         <v>35</v>
       </c>
-      <c r="N32" s="6">
+      <c r="N32" s="4">
         <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A33" s="5">
+      <c r="A33" s="3">
         <v>3031</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="5">
-        <v>32</v>
-      </c>
-      <c r="D33" s="5">
-        <v>8</v>
-      </c>
-      <c r="E33" s="6">
+      <c r="C33" s="3">
+        <v>32</v>
+      </c>
+      <c r="D33" s="3">
+        <v>8</v>
+      </c>
+      <c r="E33" s="4">
         <v>34</v>
       </c>
-      <c r="F33" s="6">
-        <v>8</v>
-      </c>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6">
+      <c r="F33" s="4">
+        <v>8</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4">
+        <v>34</v>
+      </c>
+      <c r="J33" s="4">
+        <v>8</v>
+      </c>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4">
         <v>37</v>
       </c>
-      <c r="N33" s="6">
+      <c r="N33" s="4">
         <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A34" s="5">
+      <c r="A34" s="3">
         <v>3032</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="3">
         <v>23</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="3">
         <v>4</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="4">
         <v>31</v>
       </c>
-      <c r="F34" s="6">
-        <v>8</v>
-      </c>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6">
+      <c r="F34" s="4">
+        <v>8</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4">
+        <v>35</v>
+      </c>
+      <c r="J34" s="4">
+        <v>10</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4">
         <v>29</v>
       </c>
-      <c r="N34" s="6">
+      <c r="N34" s="4">
         <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A35" s="5">
+      <c r="A35" s="3">
         <v>3033</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="3">
         <v>38</v>
       </c>
-      <c r="D35" s="5">
-        <v>10</v>
-      </c>
-      <c r="E35" s="6">
+      <c r="D35" s="3">
+        <v>10</v>
+      </c>
+      <c r="E35" s="4">
         <v>37</v>
       </c>
-      <c r="F35" s="6">
-        <v>8</v>
-      </c>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6">
+      <c r="F35" s="4">
+        <v>8</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4">
+        <v>39</v>
+      </c>
+      <c r="J35" s="4">
+        <v>10</v>
+      </c>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4">
         <v>36</v>
       </c>
-      <c r="N35" s="6">
+      <c r="N35" s="4">
         <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A36" s="5">
+      <c r="A36" s="3">
         <v>3034</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="3">
         <v>38</v>
       </c>
-      <c r="D36" s="5">
-        <v>10</v>
-      </c>
-      <c r="E36" s="6">
+      <c r="D36" s="3">
+        <v>10</v>
+      </c>
+      <c r="E36" s="4">
         <v>33</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="4">
         <v>5</v>
       </c>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="6">
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4">
+        <v>38</v>
+      </c>
+      <c r="J36" s="4">
+        <v>10</v>
+      </c>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4">
         <v>27</v>
       </c>
-      <c r="N36" s="6">
+      <c r="N36" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A37" s="5">
+      <c r="A37" s="3">
         <v>3035</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37" s="3">
         <v>38</v>
       </c>
-      <c r="D37" s="5">
-        <v>10</v>
-      </c>
-      <c r="E37" s="6">
+      <c r="D37" s="3">
+        <v>10</v>
+      </c>
+      <c r="E37" s="4">
         <v>40</v>
       </c>
-      <c r="F37" s="6">
-        <v>10</v>
-      </c>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6">
+      <c r="F37" s="4">
+        <v>10</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4">
         <v>40</v>
       </c>
-      <c r="N37" s="6">
+      <c r="J37" s="4">
+        <v>10</v>
+      </c>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4">
+        <v>40</v>
+      </c>
+      <c r="N37" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A38" s="5">
+      <c r="A38" s="3">
         <v>3036</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38" s="3">
         <v>29</v>
       </c>
-      <c r="D38" s="5">
-        <v>7</v>
-      </c>
-      <c r="E38" s="6">
+      <c r="D38" s="3">
+        <v>7</v>
+      </c>
+      <c r="E38" s="4">
         <v>31</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38" s="4">
         <v>9</v>
       </c>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6">
-        <v>32</v>
-      </c>
-      <c r="N38" s="6">
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4">
+        <v>36</v>
+      </c>
+      <c r="J38" s="4">
+        <v>10</v>
+      </c>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4">
+        <v>32</v>
+      </c>
+      <c r="N38" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A39" s="5">
+      <c r="A39" s="3">
         <v>3037</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C39" s="3">
         <v>38</v>
       </c>
-      <c r="D39" s="5">
-        <v>10</v>
-      </c>
-      <c r="E39" s="6">
+      <c r="D39" s="3">
+        <v>10</v>
+      </c>
+      <c r="E39" s="4">
         <v>21</v>
       </c>
-      <c r="F39" s="6">
-        <v>6</v>
-      </c>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6">
+      <c r="F39" s="4">
+        <v>6</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4">
         <v>27</v>
       </c>
-      <c r="N39" s="6">
+      <c r="J39" s="4">
+        <v>10</v>
+      </c>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4">
+        <v>27</v>
+      </c>
+      <c r="N39" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A40" s="5">
+      <c r="A40" s="3">
         <v>3038</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="5">
-        <v>32</v>
-      </c>
-      <c r="D40" s="5">
-        <v>8</v>
-      </c>
-      <c r="E40" s="6">
+      <c r="C40" s="3">
+        <v>32</v>
+      </c>
+      <c r="D40" s="3">
+        <v>8</v>
+      </c>
+      <c r="E40" s="4">
         <v>30</v>
       </c>
-      <c r="F40" s="6">
-        <v>8</v>
-      </c>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="6">
-        <v>32</v>
-      </c>
-      <c r="N40" s="6">
+      <c r="F40" s="4">
+        <v>8</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4">
+        <v>31</v>
+      </c>
+      <c r="J40" s="4">
+        <v>7</v>
+      </c>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4">
+        <v>32</v>
+      </c>
+      <c r="N40" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A41" s="5">
+      <c r="A41" s="3">
         <v>3039</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C41" s="5">
-        <v>32</v>
-      </c>
-      <c r="D41" s="5">
-        <v>8</v>
-      </c>
-      <c r="E41" s="6">
+      <c r="C41" s="3">
+        <v>32</v>
+      </c>
+      <c r="D41" s="3">
+        <v>8</v>
+      </c>
+      <c r="E41" s="4">
         <v>33</v>
       </c>
-      <c r="F41" s="6">
-        <v>7</v>
-      </c>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6">
-        <v>32</v>
-      </c>
-      <c r="N41" s="6">
+      <c r="F41" s="4">
+        <v>7</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4">
+        <v>35</v>
+      </c>
+      <c r="J41" s="4">
+        <v>10</v>
+      </c>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4">
+        <v>32</v>
+      </c>
+      <c r="N41" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A42" s="5">
+      <c r="A42" s="3">
         <v>3040</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="5">
-        <v>32</v>
-      </c>
-      <c r="D42" s="5">
-        <v>8</v>
-      </c>
-      <c r="E42" s="6">
+      <c r="C42" s="3">
+        <v>32</v>
+      </c>
+      <c r="D42" s="3">
+        <v>8</v>
+      </c>
+      <c r="E42" s="4">
         <v>15</v>
       </c>
-      <c r="F42" s="6">
-        <v>6</v>
-      </c>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6"/>
-      <c r="M42" s="6">
+      <c r="F42" s="4">
+        <v>6</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4">
+        <v>31</v>
+      </c>
+      <c r="J42" s="4">
+        <v>9</v>
+      </c>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4">
         <v>19</v>
       </c>
-      <c r="N42" s="6">
+      <c r="N42" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A43" s="5">
+      <c r="A43" s="3">
         <v>3041</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43" s="3">
         <v>26</v>
       </c>
-      <c r="D43" s="5">
-        <v>6</v>
-      </c>
-      <c r="E43" s="6">
+      <c r="D43" s="3">
+        <v>6</v>
+      </c>
+      <c r="E43" s="4">
         <v>17</v>
       </c>
-      <c r="F43" s="6">
-        <v>6</v>
-      </c>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="6">
+      <c r="F43" s="4">
+        <v>6</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4">
+        <v>34</v>
+      </c>
+      <c r="J43" s="4">
+        <v>7</v>
+      </c>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4">
         <v>22</v>
       </c>
-      <c r="N43" s="6">
+      <c r="N43" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A44" s="5">
+      <c r="A44" s="3">
         <v>3042</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C44" s="3">
         <v>38</v>
       </c>
-      <c r="D44" s="5">
-        <v>10</v>
-      </c>
-      <c r="E44" s="6">
+      <c r="D44" s="3">
+        <v>10</v>
+      </c>
+      <c r="E44" s="4">
         <v>37</v>
       </c>
-      <c r="F44" s="6">
-        <v>8</v>
-      </c>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6">
+      <c r="F44" s="4">
+        <v>8</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4">
+        <v>37</v>
+      </c>
+      <c r="J44" s="4">
+        <v>10</v>
+      </c>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4">
         <v>40</v>
       </c>
-      <c r="N44" s="6">
+      <c r="N44" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A45" s="5">
+      <c r="A45" s="3">
         <v>3043</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="5">
-        <v>32</v>
-      </c>
-      <c r="D45" s="5">
-        <v>8</v>
-      </c>
-      <c r="E45" s="6">
+      <c r="C45" s="3">
+        <v>32</v>
+      </c>
+      <c r="D45" s="3">
+        <v>8</v>
+      </c>
+      <c r="E45" s="4">
         <v>25</v>
       </c>
-      <c r="F45" s="6">
+      <c r="F45" s="4">
         <v>0</v>
       </c>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6">
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4">
+        <v>36</v>
+      </c>
+      <c r="J45" s="4">
+        <v>9</v>
+      </c>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4">
         <v>25</v>
       </c>
-      <c r="N45" s="6">
+      <c r="N45" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A46" s="5">
+      <c r="A46" s="3">
         <v>3044</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="5">
+      <c r="C46" s="3">
         <v>38</v>
       </c>
-      <c r="D46" s="5">
-        <v>10</v>
-      </c>
-      <c r="E46" s="6">
-        <v>32</v>
-      </c>
-      <c r="F46" s="6">
-        <v>7</v>
-      </c>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="6">
+      <c r="D46" s="3">
+        <v>10</v>
+      </c>
+      <c r="E46" s="4">
+        <v>32</v>
+      </c>
+      <c r="F46" s="4">
+        <v>7</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4">
+        <v>39</v>
+      </c>
+      <c r="J46" s="4">
+        <v>10</v>
+      </c>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4">
         <v>30</v>
       </c>
-      <c r="N46" s="6">
+      <c r="N46" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A47" s="5">
+      <c r="A47" s="3">
         <v>3045</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C47" s="5">
-        <v>32</v>
-      </c>
-      <c r="D47" s="5">
-        <v>8</v>
-      </c>
-      <c r="E47" s="6">
+      <c r="C47" s="3">
+        <v>32</v>
+      </c>
+      <c r="D47" s="3">
+        <v>8</v>
+      </c>
+      <c r="E47" s="4">
         <v>33</v>
       </c>
-      <c r="F47" s="6">
-        <v>6</v>
-      </c>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="6">
+      <c r="F47" s="4">
+        <v>6</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4">
+        <v>34</v>
+      </c>
+      <c r="J47" s="4">
+        <v>8</v>
+      </c>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4">
         <v>26</v>
       </c>
-      <c r="N47" s="6">
+      <c r="N47" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A48" s="5">
+      <c r="A48" s="3">
         <v>3046</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C48" s="3">
         <v>14</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="3">
         <v>0</v>
       </c>
-      <c r="E48" s="6">
+      <c r="E48" s="4">
         <v>22</v>
       </c>
-      <c r="F48" s="6">
+      <c r="F48" s="4">
         <v>0</v>
       </c>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="6">
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4">
+        <v>32</v>
+      </c>
+      <c r="J48" s="4">
+        <v>8</v>
+      </c>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4">
         <v>23</v>
       </c>
-      <c r="N48" s="6">
+      <c r="N48" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A49" s="5">
+      <c r="A49" s="3">
         <v>3047</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C49" s="5">
+      <c r="C49" s="3">
         <v>29</v>
       </c>
-      <c r="D49" s="5">
-        <v>7</v>
-      </c>
-      <c r="E49" s="6">
+      <c r="D49" s="3">
+        <v>7</v>
+      </c>
+      <c r="E49" s="4">
         <v>30</v>
       </c>
-      <c r="F49" s="6">
+      <c r="F49" s="4">
         <v>4</v>
       </c>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="6">
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4">
+        <v>29</v>
+      </c>
+      <c r="J49" s="4">
+        <v>9</v>
+      </c>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4">
         <v>27</v>
       </c>
-      <c r="N49" s="6">
+      <c r="N49" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A50" s="5">
+      <c r="A50" s="3">
         <v>3048</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C50" s="5">
+      <c r="C50" s="3">
         <v>29</v>
       </c>
-      <c r="D50" s="5">
-        <v>7</v>
-      </c>
-      <c r="E50" s="6">
+      <c r="D50" s="3">
+        <v>7</v>
+      </c>
+      <c r="E50" s="4">
         <v>25</v>
       </c>
-      <c r="F50" s="6">
+      <c r="F50" s="4">
         <v>9</v>
       </c>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="6">
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4">
+        <v>29</v>
+      </c>
+      <c r="J50" s="4">
+        <v>10</v>
+      </c>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4">
         <v>26</v>
       </c>
-      <c r="N50" s="6">
+      <c r="N50" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A51" s="5">
+      <c r="A51" s="3">
         <v>3049</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C51" s="5">
+      <c r="C51" s="3">
         <v>23</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51" s="3">
         <v>5</v>
       </c>
-      <c r="E51" s="6">
+      <c r="E51" s="4">
         <v>26</v>
       </c>
-      <c r="F51" s="6">
+      <c r="F51" s="4">
         <v>4</v>
       </c>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="6">
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4">
+        <v>29</v>
+      </c>
+      <c r="J51" s="4">
+        <v>9</v>
+      </c>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4">
         <v>24</v>
       </c>
-      <c r="N51" s="6">
+      <c r="N51" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A52" s="5">
+      <c r="A52" s="3">
         <v>3050</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C52" s="5">
+      <c r="C52" s="3">
         <v>29</v>
       </c>
-      <c r="D52" s="5">
-        <v>7</v>
-      </c>
-      <c r="E52" s="6">
-        <v>32</v>
-      </c>
-      <c r="F52" s="6">
-        <v>7</v>
-      </c>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
-      <c r="M52" s="6">
+      <c r="D52" s="3">
+        <v>7</v>
+      </c>
+      <c r="E52" s="4">
+        <v>32</v>
+      </c>
+      <c r="F52" s="4">
+        <v>7</v>
+      </c>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4">
+        <v>33</v>
+      </c>
+      <c r="J52" s="4">
+        <v>9</v>
+      </c>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4">
         <v>34</v>
       </c>
-      <c r="N52" s="6">
+      <c r="N52" s="4">
         <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A53" s="5">
+      <c r="A53" s="3">
         <v>3051</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C53" s="5">
-        <v>32</v>
-      </c>
-      <c r="D53" s="5">
-        <v>8</v>
-      </c>
-      <c r="E53" s="6">
+      <c r="C53" s="3">
+        <v>32</v>
+      </c>
+      <c r="D53" s="3">
+        <v>8</v>
+      </c>
+      <c r="E53" s="4">
         <v>22</v>
       </c>
-      <c r="F53" s="6">
+      <c r="F53" s="4">
         <v>4</v>
       </c>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="6">
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4">
+        <v>24</v>
+      </c>
+      <c r="J53" s="4">
+        <v>9</v>
+      </c>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4">
         <v>30</v>
       </c>
-      <c r="N53" s="6">
+      <c r="N53" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A54" s="5">
+      <c r="A54" s="3">
         <v>3052</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C54" s="5">
-        <v>32</v>
-      </c>
-      <c r="D54" s="5">
-        <v>8</v>
-      </c>
-      <c r="E54" s="6">
+      <c r="C54" s="3">
+        <v>32</v>
+      </c>
+      <c r="D54" s="3">
+        <v>8</v>
+      </c>
+      <c r="E54" s="4">
         <v>20</v>
       </c>
-      <c r="F54" s="6">
-        <v>7</v>
-      </c>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="6">
+      <c r="F54" s="4">
+        <v>7</v>
+      </c>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4">
+        <v>29</v>
+      </c>
+      <c r="J54" s="4">
+        <v>9</v>
+      </c>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4">
         <v>26</v>
       </c>
-      <c r="N54" s="6">
+      <c r="N54" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A55" s="5">
+      <c r="A55" s="3">
         <v>3053</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C55" s="5">
+      <c r="C55" s="3">
         <v>26</v>
       </c>
-      <c r="D55" s="5">
-        <v>6</v>
-      </c>
-      <c r="E55" s="6">
+      <c r="D55" s="3">
+        <v>6</v>
+      </c>
+      <c r="E55" s="4">
         <v>21</v>
       </c>
-      <c r="F55" s="6">
-        <v>6</v>
-      </c>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6">
+      <c r="F55" s="4">
+        <v>6</v>
+      </c>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4">
+        <v>35</v>
+      </c>
+      <c r="J55" s="4">
+        <v>8</v>
+      </c>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4">
         <v>26</v>
       </c>
-      <c r="N55" s="6">
+      <c r="N55" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A56" s="5">
+      <c r="A56" s="3">
         <v>3054</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C56" s="5">
+      <c r="C56" s="3">
         <v>35</v>
       </c>
-      <c r="D56" s="5">
+      <c r="D56" s="3">
         <v>9</v>
       </c>
-      <c r="E56" s="6">
+      <c r="E56" s="4">
         <v>21</v>
       </c>
-      <c r="F56" s="6">
-        <v>8</v>
-      </c>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="6">
+      <c r="F56" s="4">
+        <v>8</v>
+      </c>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4">
+        <v>30</v>
+      </c>
+      <c r="J56" s="4">
+        <v>8</v>
+      </c>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4">
         <v>27</v>
       </c>
-      <c r="N56" s="6">
+      <c r="N56" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A57" s="5">
+      <c r="A57" s="3">
         <v>3055</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C57" s="5">
+      <c r="C57" s="3">
         <v>38</v>
       </c>
-      <c r="D57" s="5">
-        <v>10</v>
-      </c>
-      <c r="E57" s="6">
+      <c r="D57" s="3">
+        <v>10</v>
+      </c>
+      <c r="E57" s="4">
         <v>35</v>
       </c>
-      <c r="F57" s="6">
-        <v>8</v>
-      </c>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="6"/>
-      <c r="M57" s="6">
+      <c r="F57" s="4">
+        <v>8</v>
+      </c>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4">
         <v>40</v>
       </c>
-      <c r="N57" s="6">
+      <c r="J57" s="4">
+        <v>10</v>
+      </c>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4">
+        <v>40</v>
+      </c>
+      <c r="N57" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A58" s="5">
+      <c r="A58" s="3">
         <v>3056</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C58" s="5">
+      <c r="C58" s="3">
         <v>38</v>
       </c>
-      <c r="D58" s="5">
-        <v>10</v>
-      </c>
-      <c r="E58" s="6">
+      <c r="D58" s="3">
+        <v>10</v>
+      </c>
+      <c r="E58" s="4">
         <v>26</v>
       </c>
-      <c r="F58" s="6">
-        <v>7</v>
-      </c>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="6">
+      <c r="F58" s="4">
+        <v>7</v>
+      </c>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4">
+        <v>32</v>
+      </c>
+      <c r="J58" s="4">
+        <v>8</v>
+      </c>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4">
         <v>29</v>
       </c>
-      <c r="N58" s="6">
+      <c r="N58" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A59" s="5">
+      <c r="A59" s="3">
         <v>3057</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C59" s="5">
-        <v>32</v>
-      </c>
-      <c r="D59" s="5">
-        <v>8</v>
-      </c>
-      <c r="E59" s="6">
+      <c r="C59" s="3">
+        <v>32</v>
+      </c>
+      <c r="D59" s="3">
+        <v>8</v>
+      </c>
+      <c r="E59" s="4">
         <v>36</v>
       </c>
-      <c r="F59" s="6">
-        <v>8</v>
-      </c>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6">
+      <c r="F59" s="4">
+        <v>8</v>
+      </c>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4">
+        <v>40</v>
+      </c>
+      <c r="J59" s="4">
+        <v>10</v>
+      </c>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4">
         <v>36</v>
       </c>
-      <c r="N59" s="6">
+      <c r="N59" s="4">
         <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A60" s="5">
+      <c r="A60" s="3">
         <v>3058</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C60" s="5">
-        <v>32</v>
-      </c>
-      <c r="D60" s="5">
-        <v>8</v>
-      </c>
-      <c r="E60" s="6">
+      <c r="C60" s="3">
+        <v>32</v>
+      </c>
+      <c r="D60" s="3">
+        <v>8</v>
+      </c>
+      <c r="E60" s="4">
         <v>28</v>
       </c>
-      <c r="F60" s="6">
-        <v>7</v>
-      </c>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6">
+      <c r="F60" s="4">
+        <v>7</v>
+      </c>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4">
+        <v>34</v>
+      </c>
+      <c r="J60" s="4">
+        <v>10</v>
+      </c>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4">
         <v>30</v>
       </c>
-      <c r="N60" s="6">
+      <c r="N60" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A61" s="5">
+      <c r="A61" s="3">
         <v>3059</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C61" s="5">
-        <v>32</v>
-      </c>
-      <c r="D61" s="5">
-        <v>8</v>
-      </c>
-      <c r="E61" s="6">
+      <c r="C61" s="3">
+        <v>32</v>
+      </c>
+      <c r="D61" s="3">
+        <v>8</v>
+      </c>
+      <c r="E61" s="4">
         <v>27</v>
       </c>
-      <c r="F61" s="6">
-        <v>7</v>
-      </c>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="6"/>
-      <c r="M61" s="6">
+      <c r="F61" s="4">
+        <v>7</v>
+      </c>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4">
+        <v>32</v>
+      </c>
+      <c r="J61" s="4">
+        <v>10</v>
+      </c>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4">
         <v>26</v>
       </c>
-      <c r="N61" s="6">
+      <c r="N61" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A62" s="5">
+      <c r="A62" s="3">
         <v>3060</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C62" s="5">
+      <c r="C62" s="3">
         <v>23</v>
       </c>
-      <c r="D62" s="5">
+      <c r="D62" s="3">
         <v>4</v>
       </c>
-      <c r="E62" s="6">
+      <c r="E62" s="4">
         <v>22</v>
       </c>
-      <c r="F62" s="6">
-        <v>6</v>
-      </c>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="6"/>
-      <c r="M62" s="6">
+      <c r="F62" s="4">
+        <v>6</v>
+      </c>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4">
+        <v>26</v>
+      </c>
+      <c r="J62" s="4">
+        <v>9</v>
+      </c>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4">
         <v>25</v>
       </c>
-      <c r="N62" s="6">
+      <c r="N62" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A63" s="5">
+      <c r="A63" s="3">
         <v>3061</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C63" s="5">
+      <c r="C63" s="3">
         <v>35</v>
       </c>
-      <c r="D63" s="5">
+      <c r="D63" s="3">
         <v>9</v>
       </c>
-      <c r="E63" s="6">
+      <c r="E63" s="4">
         <v>31</v>
       </c>
-      <c r="F63" s="6">
-        <v>6</v>
-      </c>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="6">
+      <c r="F63" s="4">
+        <v>6</v>
+      </c>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4">
+        <v>30</v>
+      </c>
+      <c r="J63" s="4">
+        <v>10</v>
+      </c>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4">
         <v>25</v>
       </c>
-      <c r="N63" s="6">
+      <c r="N63" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A64" s="5">
+      <c r="A64" s="3">
         <v>3062</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B64" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C64" s="5">
+      <c r="C64" s="3">
         <v>29</v>
       </c>
-      <c r="D64" s="5">
-        <v>7</v>
-      </c>
-      <c r="E64" s="6">
+      <c r="D64" s="3">
+        <v>7</v>
+      </c>
+      <c r="E64" s="4">
         <v>28</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F64" s="4">
         <v>5</v>
       </c>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6"/>
-      <c r="L64" s="6"/>
-      <c r="M64" s="6">
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4">
+        <v>30</v>
+      </c>
+      <c r="J64" s="4">
+        <v>10</v>
+      </c>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4">
         <v>28</v>
       </c>
-      <c r="N64" s="6">
+      <c r="N64" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A65" s="5">
+      <c r="A65" s="3">
         <v>3063</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B65" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C65" s="5">
+      <c r="C65" s="3">
         <v>38</v>
       </c>
-      <c r="D65" s="5">
-        <v>10</v>
-      </c>
-      <c r="E65" s="6">
+      <c r="D65" s="3">
+        <v>10</v>
+      </c>
+      <c r="E65" s="4">
         <v>25</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F65" s="4">
         <v>5</v>
       </c>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="6"/>
-      <c r="M65" s="6">
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4">
+        <v>28</v>
+      </c>
+      <c r="J65" s="4">
+        <v>8</v>
+      </c>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4">
         <v>27</v>
       </c>
-      <c r="N65" s="6">
+      <c r="N65" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A66" s="5">
+      <c r="A66" s="3">
         <v>3064</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C66" s="5">
+      <c r="C66" s="3">
         <v>35</v>
       </c>
-      <c r="D66" s="5">
+      <c r="D66" s="3">
         <v>9</v>
       </c>
-      <c r="E66" s="6">
+      <c r="E66" s="4">
         <v>33</v>
       </c>
-      <c r="F66" s="6">
-        <v>6</v>
-      </c>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
-      <c r="M66" s="6">
+      <c r="F66" s="4">
+        <v>6</v>
+      </c>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4">
+        <v>34</v>
+      </c>
+      <c r="J66" s="4">
+        <v>9</v>
+      </c>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4">
         <v>23</v>
       </c>
-      <c r="N66" s="6">
+      <c r="N66" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A67" s="5">
+      <c r="A67" s="3">
         <v>3065</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C67" s="5">
-        <v>32</v>
-      </c>
-      <c r="D67" s="5">
-        <v>8</v>
-      </c>
-      <c r="E67" s="6">
+      <c r="C67" s="3">
+        <v>32</v>
+      </c>
+      <c r="D67" s="3">
+        <v>8</v>
+      </c>
+      <c r="E67" s="4">
         <v>27</v>
       </c>
-      <c r="F67" s="6">
+      <c r="F67" s="4">
         <v>9</v>
       </c>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="6"/>
-      <c r="L67" s="6"/>
-      <c r="M67" s="6">
-        <v>32</v>
-      </c>
-      <c r="N67" s="6">
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4">
+        <v>38</v>
+      </c>
+      <c r="J67" s="4">
+        <v>10</v>
+      </c>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4">
+        <v>32</v>
+      </c>
+      <c r="N67" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A68" s="5">
+      <c r="A68" s="3">
         <v>3066</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C68" s="5">
+      <c r="C68" s="3">
         <v>38</v>
       </c>
-      <c r="D68" s="5">
-        <v>10</v>
-      </c>
-      <c r="E68" s="6">
+      <c r="D68" s="3">
+        <v>10</v>
+      </c>
+      <c r="E68" s="4">
         <v>33</v>
       </c>
-      <c r="F68" s="6">
-        <v>8</v>
-      </c>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="6"/>
-      <c r="L68" s="6"/>
-      <c r="M68" s="6">
+      <c r="F68" s="4">
+        <v>8</v>
+      </c>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4">
+        <v>38</v>
+      </c>
+      <c r="J68" s="4">
+        <v>10</v>
+      </c>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4">
         <v>36</v>
       </c>
-      <c r="N68" s="6">
+      <c r="N68" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A69" s="5">
+      <c r="A69" s="3">
         <v>3067</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C69" s="5">
-        <v>32</v>
-      </c>
-      <c r="D69" s="5">
-        <v>8</v>
-      </c>
-      <c r="E69" s="6">
+      <c r="C69" s="3">
+        <v>32</v>
+      </c>
+      <c r="D69" s="3">
+        <v>8</v>
+      </c>
+      <c r="E69" s="4">
         <v>31</v>
       </c>
-      <c r="F69" s="6">
-        <v>6</v>
-      </c>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="6"/>
-      <c r="L69" s="6"/>
-      <c r="M69" s="6">
+      <c r="F69" s="4">
+        <v>6</v>
+      </c>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4">
+        <v>36</v>
+      </c>
+      <c r="J69" s="4">
+        <v>10</v>
+      </c>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4">
         <v>33</v>
       </c>
-      <c r="N69" s="6">
+      <c r="N69" s="4">
         <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A70" s="5">
+      <c r="A70" s="3">
         <v>3068</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B70" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C70" s="5">
+      <c r="C70" s="3">
         <v>38</v>
       </c>
-      <c r="D70" s="5">
-        <v>10</v>
-      </c>
-      <c r="E70" s="6">
+      <c r="D70" s="3">
+        <v>10</v>
+      </c>
+      <c r="E70" s="4">
         <v>36</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F70" s="4">
         <v>4</v>
       </c>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="6"/>
-      <c r="L70" s="6"/>
-      <c r="M70" s="6">
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4">
+        <v>39</v>
+      </c>
+      <c r="J70" s="4">
+        <v>10</v>
+      </c>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4">
         <v>37</v>
       </c>
-      <c r="N70" s="6">
+      <c r="N70" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A71" s="5">
+      <c r="A71" s="3">
         <v>3069</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B71" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C71" s="5">
+      <c r="C71" s="3">
         <v>26</v>
       </c>
-      <c r="D71" s="5">
-        <v>6</v>
-      </c>
-      <c r="E71" s="6">
+      <c r="D71" s="3">
+        <v>6</v>
+      </c>
+      <c r="E71" s="4">
         <v>30</v>
       </c>
-      <c r="F71" s="6">
-        <v>7</v>
-      </c>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="6"/>
-      <c r="L71" s="6"/>
-      <c r="M71" s="6">
+      <c r="F71" s="4">
+        <v>7</v>
+      </c>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4">
+        <v>37</v>
+      </c>
+      <c r="J71" s="4">
+        <v>9</v>
+      </c>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4">
         <v>25</v>
       </c>
-      <c r="N71" s="6">
+      <c r="N71" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A72" s="5">
+      <c r="A72" s="3">
         <v>3070</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C72" s="5">
-        <v>32</v>
-      </c>
-      <c r="D72" s="5">
-        <v>8</v>
-      </c>
-      <c r="E72" s="6">
-        <v>32</v>
-      </c>
-      <c r="F72" s="6">
-        <v>6</v>
-      </c>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="6"/>
-      <c r="M72" s="6">
+      <c r="C72" s="3">
+        <v>32</v>
+      </c>
+      <c r="D72" s="3">
+        <v>8</v>
+      </c>
+      <c r="E72" s="4">
+        <v>32</v>
+      </c>
+      <c r="F72" s="4">
+        <v>6</v>
+      </c>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4">
+        <v>28</v>
+      </c>
+      <c r="J72" s="4">
+        <v>10</v>
+      </c>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4">
         <v>29</v>
       </c>
-      <c r="N72" s="6">
+      <c r="N72" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A73" s="5">
+      <c r="A73" s="3">
         <v>3071</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B73" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C73" s="5">
+      <c r="C73" s="3">
         <v>35</v>
       </c>
-      <c r="D73" s="5">
+      <c r="D73" s="3">
         <v>9</v>
       </c>
-      <c r="E73" s="6">
+      <c r="E73" s="4">
         <v>21</v>
       </c>
-      <c r="F73" s="6">
-        <v>7</v>
-      </c>
-      <c r="G73" s="6"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="6"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="6"/>
-      <c r="L73" s="6"/>
-      <c r="M73" s="6">
+      <c r="F73" s="4">
+        <v>7</v>
+      </c>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4">
+        <v>31</v>
+      </c>
+      <c r="J73" s="4">
+        <v>10</v>
+      </c>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="4">
         <v>24</v>
       </c>
-      <c r="N73" s="6">
+      <c r="N73" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A74" s="5">
+      <c r="A74" s="3">
         <v>3072</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C74" s="5">
+      <c r="C74" s="3">
         <v>0</v>
       </c>
-      <c r="D74" s="5">
+      <c r="D74" s="3">
         <v>0</v>
       </c>
-      <c r="E74" s="6">
+      <c r="E74" s="4">
         <v>21</v>
       </c>
-      <c r="F74" s="6">
+      <c r="F74" s="4">
         <v>0</v>
       </c>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
-      <c r="M74" s="6">
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4">
+        <v>27</v>
+      </c>
+      <c r="J74" s="4">
+        <v>6</v>
+      </c>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4">
         <v>15</v>
       </c>
-      <c r="N74" s="6">
+      <c r="N74" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A75" s="5">
+      <c r="A75" s="3">
         <v>3073</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="B75" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C75" s="5">
-        <v>32</v>
-      </c>
-      <c r="D75" s="5">
-        <v>8</v>
-      </c>
-      <c r="E75" s="6">
+      <c r="C75" s="3">
+        <v>32</v>
+      </c>
+      <c r="D75" s="3">
+        <v>8</v>
+      </c>
+      <c r="E75" s="4">
         <v>35</v>
       </c>
-      <c r="F75" s="6">
-        <v>8</v>
-      </c>
-      <c r="G75" s="6"/>
-      <c r="H75" s="6"/>
-      <c r="I75" s="6"/>
-      <c r="J75" s="6"/>
-      <c r="K75" s="6"/>
-      <c r="L75" s="6"/>
-      <c r="M75" s="6">
+      <c r="F75" s="4">
+        <v>8</v>
+      </c>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4">
+        <v>35</v>
+      </c>
+      <c r="J75" s="4">
+        <v>10</v>
+      </c>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4">
         <v>40</v>
       </c>
-      <c r="N75" s="6">
+      <c r="N75" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A76" s="5">
+      <c r="A76" s="3">
         <v>3074</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C76" s="5">
+      <c r="C76" s="3">
         <v>14</v>
       </c>
-      <c r="D76" s="5">
+      <c r="D76" s="3">
         <v>0</v>
       </c>
-      <c r="E76" s="6">
+      <c r="E76" s="4">
         <v>25</v>
       </c>
-      <c r="F76" s="6">
+      <c r="F76" s="4">
         <v>5</v>
       </c>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
-      <c r="K76" s="6"/>
-      <c r="L76" s="6"/>
-      <c r="M76" s="6">
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4">
+        <v>35</v>
+      </c>
+      <c r="J76" s="4">
+        <v>10</v>
+      </c>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4">
         <v>24</v>
       </c>
-      <c r="N76" s="6">
+      <c r="N76" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A77" s="5">
+      <c r="A77" s="3">
         <v>3075</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B77" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C77" s="5">
+      <c r="C77" s="3">
         <v>35</v>
       </c>
-      <c r="D77" s="5">
+      <c r="D77" s="3">
         <v>9</v>
       </c>
-      <c r="E77" s="6">
+      <c r="E77" s="4">
         <v>24</v>
       </c>
-      <c r="F77" s="6">
+      <c r="F77" s="4">
         <v>5</v>
       </c>
-      <c r="G77" s="6"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="6"/>
-      <c r="L77" s="6"/>
-      <c r="M77" s="6">
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4">
+        <v>34</v>
+      </c>
+      <c r="J77" s="4">
+        <v>10</v>
+      </c>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4">
         <v>26</v>
       </c>
-      <c r="N77" s="6">
+      <c r="N77" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A78" s="5">
+      <c r="A78" s="3">
         <v>3076</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B78" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C78" s="5">
+      <c r="C78" s="3">
         <v>29</v>
       </c>
-      <c r="D78" s="5">
-        <v>7</v>
-      </c>
-      <c r="E78" s="6">
+      <c r="D78" s="3">
+        <v>7</v>
+      </c>
+      <c r="E78" s="4">
         <v>26</v>
       </c>
-      <c r="F78" s="6">
-        <v>6</v>
-      </c>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6"/>
-      <c r="L78" s="6"/>
-      <c r="M78" s="6">
+      <c r="F78" s="4">
+        <v>6</v>
+      </c>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4">
+        <v>30</v>
+      </c>
+      <c r="J78" s="4">
+        <v>10</v>
+      </c>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4">
         <v>23</v>
       </c>
-      <c r="N78" s="6">
+      <c r="N78" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A79" s="5">
+      <c r="A79" s="3">
         <v>3077</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C79" s="5">
+      <c r="C79" s="3">
         <v>23</v>
       </c>
-      <c r="D79" s="5">
+      <c r="D79" s="3">
         <v>3</v>
       </c>
-      <c r="E79" s="6">
+      <c r="E79" s="4">
         <v>20</v>
       </c>
-      <c r="F79" s="6">
-        <v>6</v>
-      </c>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
-      <c r="J79" s="6"/>
-      <c r="K79" s="6"/>
-      <c r="L79" s="6"/>
-      <c r="M79" s="6">
+      <c r="F79" s="4">
+        <v>6</v>
+      </c>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4">
+        <v>32</v>
+      </c>
+      <c r="J79" s="4">
+        <v>8</v>
+      </c>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4">
         <v>22</v>
       </c>
-      <c r="N79" s="6">
+      <c r="N79" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A80" s="5">
+      <c r="A80" s="3">
         <v>3078</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="B80" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C80" s="5">
+      <c r="C80" s="3">
         <v>14</v>
       </c>
-      <c r="D80" s="5">
+      <c r="D80" s="3">
         <v>0</v>
       </c>
-      <c r="E80" s="6">
+      <c r="E80" s="4">
         <v>22</v>
       </c>
-      <c r="F80" s="6">
-        <v>6</v>
-      </c>
-      <c r="G80" s="6"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="6"/>
-      <c r="K80" s="6"/>
-      <c r="L80" s="6"/>
-      <c r="M80" s="6">
+      <c r="F80" s="4">
+        <v>6</v>
+      </c>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4">
+        <v>31</v>
+      </c>
+      <c r="J80" s="4">
+        <v>7</v>
+      </c>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="4">
         <v>20</v>
       </c>
-      <c r="N80" s="6">
+      <c r="N80" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A81" s="5">
+      <c r="A81" s="3">
         <v>3079</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="B81" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C81" s="5">
+      <c r="C81" s="3">
         <v>26</v>
       </c>
-      <c r="D81" s="5">
-        <v>6</v>
-      </c>
-      <c r="E81" s="6">
+      <c r="D81" s="3">
+        <v>6</v>
+      </c>
+      <c r="E81" s="4">
         <v>30</v>
       </c>
-      <c r="F81" s="6">
-        <v>6</v>
-      </c>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6"/>
-      <c r="L81" s="6"/>
-      <c r="M81" s="6">
+      <c r="F81" s="4">
+        <v>6</v>
+      </c>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4">
+        <v>35</v>
+      </c>
+      <c r="J81" s="4">
+        <v>9</v>
+      </c>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="4">
         <v>26</v>
       </c>
-      <c r="N81" s="6">
+      <c r="N81" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A82" s="5">
+      <c r="A82" s="3">
         <v>3080</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C82" s="5">
+      <c r="C82" s="3">
         <v>26</v>
       </c>
-      <c r="D82" s="5">
-        <v>6</v>
-      </c>
-      <c r="E82" s="6">
+      <c r="D82" s="3">
+        <v>6</v>
+      </c>
+      <c r="E82" s="4">
         <v>27</v>
       </c>
-      <c r="F82" s="6">
-        <v>7</v>
-      </c>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6"/>
-      <c r="J82" s="6"/>
-      <c r="K82" s="6"/>
-      <c r="L82" s="6"/>
-      <c r="M82" s="6">
+      <c r="F82" s="4">
+        <v>7</v>
+      </c>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4">
+        <v>29</v>
+      </c>
+      <c r="J82" s="4">
+        <v>9</v>
+      </c>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="4">
         <v>24</v>
       </c>
-      <c r="N82" s="6">
+      <c r="N82" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="83" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A83" s="5">
+      <c r="A83" s="3">
         <v>3081</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="B83" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C83" s="5">
-        <v>32</v>
-      </c>
-      <c r="D83" s="5">
-        <v>8</v>
-      </c>
-      <c r="E83" s="6">
+      <c r="C83" s="3">
+        <v>32</v>
+      </c>
+      <c r="D83" s="3">
+        <v>8</v>
+      </c>
+      <c r="E83" s="4">
         <v>34</v>
       </c>
-      <c r="F83" s="6">
-        <v>6</v>
-      </c>
-      <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="6"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6"/>
-      <c r="L83" s="6"/>
-      <c r="M83" s="6">
+      <c r="F83" s="4">
+        <v>6</v>
+      </c>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4">
+        <v>32</v>
+      </c>
+      <c r="J83" s="4">
+        <v>6</v>
+      </c>
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="4">
         <v>26</v>
       </c>
-      <c r="N83" s="6">
+      <c r="N83" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="84" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A84" s="5">
+      <c r="A84" s="3">
         <v>3082</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="B84" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C84" s="5">
+      <c r="C84" s="3">
         <v>14</v>
       </c>
-      <c r="D84" s="5">
+      <c r="D84" s="3">
         <v>0</v>
       </c>
-      <c r="E84" s="6">
+      <c r="E84" s="4">
         <v>14</v>
       </c>
-      <c r="F84" s="6">
+      <c r="F84" s="4">
         <v>0</v>
       </c>
-      <c r="G84" s="6"/>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6"/>
-      <c r="J84" s="6"/>
-      <c r="K84" s="6"/>
-      <c r="L84" s="6"/>
-      <c r="M84" s="6">
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4">
+        <v>23</v>
+      </c>
+      <c r="J84" s="4">
+        <v>7</v>
+      </c>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="4">
         <v>24</v>
       </c>
-      <c r="N84" s="6">
+      <c r="N84" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A85" s="5">
+      <c r="A85" s="3">
         <v>3083</v>
       </c>
-      <c r="B85" s="5" t="s">
+      <c r="B85" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C85" s="5">
-        <v>32</v>
-      </c>
-      <c r="D85" s="5">
-        <v>8</v>
-      </c>
-      <c r="E85" s="6">
+      <c r="C85" s="3">
+        <v>32</v>
+      </c>
+      <c r="D85" s="3">
+        <v>8</v>
+      </c>
+      <c r="E85" s="4">
         <v>35</v>
       </c>
-      <c r="F85" s="6">
-        <v>8</v>
-      </c>
-      <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
-      <c r="I85" s="6"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6"/>
-      <c r="L85" s="6"/>
-      <c r="M85" s="6">
+      <c r="F85" s="4">
+        <v>8</v>
+      </c>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4">
+        <v>40</v>
+      </c>
+      <c r="J85" s="4">
+        <v>10</v>
+      </c>
+      <c r="K85" s="4"/>
+      <c r="L85" s="4"/>
+      <c r="M85" s="4">
         <v>28</v>
       </c>
-      <c r="N85" s="6">
+      <c r="N85" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A86" s="5">
+      <c r="A86" s="3">
         <v>3084</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="B86" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C86" s="5">
-        <v>32</v>
-      </c>
-      <c r="D86" s="5">
-        <v>8</v>
-      </c>
-      <c r="E86" s="6">
+      <c r="C86" s="3">
+        <v>32</v>
+      </c>
+      <c r="D86" s="3">
+        <v>8</v>
+      </c>
+      <c r="E86" s="4">
         <v>30</v>
       </c>
-      <c r="F86" s="6">
+      <c r="F86" s="4">
         <v>9</v>
       </c>
-      <c r="G86" s="6"/>
-      <c r="H86" s="6"/>
-      <c r="I86" s="6"/>
-      <c r="J86" s="6"/>
-      <c r="K86" s="6"/>
-      <c r="L86" s="6"/>
-      <c r="M86" s="6">
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4">
+        <v>32</v>
+      </c>
+      <c r="J86" s="4">
+        <v>8</v>
+      </c>
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="4">
         <v>40</v>
       </c>
-      <c r="N86" s="6">
+      <c r="N86" s="4">
         <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A87" s="5">
+      <c r="A87" s="3">
         <v>3085</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="B87" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C87" s="5">
+      <c r="C87" s="3">
         <v>29</v>
       </c>
-      <c r="D87" s="5">
-        <v>7</v>
-      </c>
-      <c r="E87" s="6">
+      <c r="D87" s="3">
+        <v>7</v>
+      </c>
+      <c r="E87" s="4">
         <v>28</v>
       </c>
-      <c r="F87" s="6">
-        <v>6</v>
-      </c>
-      <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6"/>
-      <c r="L87" s="6"/>
-      <c r="M87" s="6">
+      <c r="F87" s="4">
+        <v>6</v>
+      </c>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+      <c r="I87" s="4">
+        <v>31</v>
+      </c>
+      <c r="J87" s="4">
+        <v>9</v>
+      </c>
+      <c r="K87" s="4"/>
+      <c r="L87" s="4"/>
+      <c r="M87" s="4">
         <v>30</v>
       </c>
-      <c r="N87" s="6">
+      <c r="N87" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A88" s="5">
+      <c r="A88" s="3">
         <v>3086</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C88" s="5">
+      <c r="C88" s="3">
         <v>23</v>
       </c>
-      <c r="D88" s="5">
+      <c r="D88" s="3">
         <v>5</v>
       </c>
-      <c r="E88" s="6">
+      <c r="E88" s="4">
         <v>14</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F88" s="4">
         <v>0</v>
       </c>
-      <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="6"/>
-      <c r="L88" s="6"/>
-      <c r="M88" s="6">
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4">
+        <v>18</v>
+      </c>
+      <c r="J88" s="4">
+        <v>7</v>
+      </c>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="4">
         <v>23</v>
       </c>
-      <c r="N88" s="6">
+      <c r="N88" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="89" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A89" s="5">
+      <c r="A89" s="3">
         <v>3087</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="B89" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C89" s="5">
+      <c r="C89" s="3">
         <v>26</v>
       </c>
-      <c r="D89" s="5">
-        <v>6</v>
-      </c>
-      <c r="E89" s="6">
+      <c r="D89" s="3">
+        <v>6</v>
+      </c>
+      <c r="E89" s="4">
         <v>28</v>
       </c>
-      <c r="F89" s="6">
-        <v>7</v>
-      </c>
-      <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
-      <c r="I89" s="6"/>
-      <c r="J89" s="6"/>
-      <c r="K89" s="6"/>
-      <c r="L89" s="6"/>
-      <c r="M89" s="6">
+      <c r="F89" s="4">
+        <v>7</v>
+      </c>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+      <c r="I89" s="4">
+        <v>38</v>
+      </c>
+      <c r="J89" s="4">
+        <v>10</v>
+      </c>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4"/>
+      <c r="M89" s="4">
         <v>27</v>
       </c>
-      <c r="N89" s="6">
+      <c r="N89" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A90" s="5">
+      <c r="A90" s="3">
         <v>3088</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C90" s="5">
+      <c r="C90" s="3">
         <v>26</v>
       </c>
-      <c r="D90" s="5">
-        <v>6</v>
-      </c>
-      <c r="E90" s="6">
+      <c r="D90" s="3">
+        <v>6</v>
+      </c>
+      <c r="E90" s="4">
         <v>28</v>
       </c>
-      <c r="F90" s="6">
-        <v>7</v>
-      </c>
-      <c r="G90" s="6"/>
-      <c r="H90" s="6"/>
-      <c r="I90" s="6"/>
-      <c r="J90" s="6"/>
-      <c r="K90" s="6"/>
-      <c r="L90" s="6"/>
-      <c r="M90" s="6">
+      <c r="F90" s="4">
+        <v>7</v>
+      </c>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4">
+        <v>32</v>
+      </c>
+      <c r="J90" s="4">
+        <v>9</v>
+      </c>
+      <c r="K90" s="4"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="4">
         <v>30</v>
       </c>
-      <c r="N90" s="6">
+      <c r="N90" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="91" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A91" s="5">
+      <c r="A91" s="3">
         <v>3089</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="B91" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C91" s="5">
-        <v>32</v>
-      </c>
-      <c r="D91" s="5">
-        <v>8</v>
-      </c>
-      <c r="E91" s="6">
+      <c r="C91" s="3">
+        <v>32</v>
+      </c>
+      <c r="D91" s="3">
+        <v>8</v>
+      </c>
+      <c r="E91" s="4">
         <v>36</v>
       </c>
-      <c r="F91" s="6">
-        <v>8</v>
-      </c>
-      <c r="G91" s="6"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="6"/>
-      <c r="J91" s="6"/>
-      <c r="K91" s="6"/>
-      <c r="L91" s="6"/>
-      <c r="M91" s="6">
-        <v>32</v>
-      </c>
-      <c r="N91" s="6">
+      <c r="F91" s="4">
+        <v>8</v>
+      </c>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="4">
+        <v>36</v>
+      </c>
+      <c r="J91" s="4">
+        <v>10</v>
+      </c>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="4">
+        <v>32</v>
+      </c>
+      <c r="N91" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A92" s="5">
+      <c r="A92" s="3">
         <v>3090</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="B92" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C92" s="5">
+      <c r="C92" s="3">
         <v>23</v>
       </c>
-      <c r="D92" s="5">
+      <c r="D92" s="3">
         <v>3</v>
       </c>
-      <c r="E92" s="6">
+      <c r="E92" s="4">
         <v>33</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F92" s="4">
         <v>4</v>
       </c>
-      <c r="G92" s="6"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="6"/>
-      <c r="J92" s="6"/>
-      <c r="K92" s="6"/>
-      <c r="L92" s="6"/>
-      <c r="M92" s="6">
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4">
+        <v>34</v>
+      </c>
+      <c r="J92" s="4">
+        <v>8</v>
+      </c>
+      <c r="K92" s="4"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="4">
         <v>27</v>
       </c>
-      <c r="N92" s="6">
+      <c r="N92" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A93" s="5">
+      <c r="A93" s="3">
         <v>3091</v>
       </c>
-      <c r="B93" s="5" t="s">
+      <c r="B93" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C93" s="5">
+      <c r="C93" s="3">
         <v>23</v>
       </c>
-      <c r="D93" s="5">
+      <c r="D93" s="3">
         <v>5</v>
       </c>
-      <c r="E93" s="6">
+      <c r="E93" s="4">
         <v>17</v>
       </c>
-      <c r="F93" s="6">
+      <c r="F93" s="4">
         <v>5</v>
       </c>
-      <c r="G93" s="6"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="6"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="6"/>
-      <c r="L93" s="6"/>
-      <c r="M93" s="6">
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="4">
+        <v>25</v>
+      </c>
+      <c r="J93" s="4">
+        <v>10</v>
+      </c>
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="4">
         <v>22</v>
       </c>
-      <c r="N93" s="6">
+      <c r="N93" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="94" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A94" s="5">
+      <c r="A94" s="3">
         <v>3092</v>
       </c>
-      <c r="B94" s="5" t="s">
+      <c r="B94" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C94" s="5">
+      <c r="C94" s="3">
         <v>14</v>
       </c>
-      <c r="D94" s="5">
+      <c r="D94" s="3">
         <v>0</v>
       </c>
-      <c r="E94" s="6">
+      <c r="E94" s="4">
         <v>33</v>
       </c>
-      <c r="F94" s="6">
-        <v>6</v>
-      </c>
-      <c r="G94" s="6"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="6"/>
-      <c r="L94" s="6"/>
-      <c r="M94" s="6">
+      <c r="F94" s="4">
+        <v>6</v>
+      </c>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4">
+        <v>36</v>
+      </c>
+      <c r="J94" s="4">
+        <v>9</v>
+      </c>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="4">
         <v>29</v>
       </c>
-      <c r="N94" s="6">
+      <c r="N94" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A95" s="5">
+      <c r="A95" s="3">
         <v>3093</v>
       </c>
-      <c r="B95" s="5" t="s">
+      <c r="B95" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C95" s="5">
+      <c r="C95" s="3">
         <v>29</v>
       </c>
-      <c r="D95" s="5">
-        <v>7</v>
-      </c>
-      <c r="E95" s="6">
+      <c r="D95" s="3">
+        <v>7</v>
+      </c>
+      <c r="E95" s="4">
         <v>22</v>
       </c>
-      <c r="F95" s="6">
-        <v>6</v>
-      </c>
-      <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="6"/>
-      <c r="J95" s="6"/>
-      <c r="K95" s="6"/>
-      <c r="L95" s="6"/>
-      <c r="M95" s="6">
+      <c r="F95" s="4">
+        <v>6</v>
+      </c>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4">
+        <v>35</v>
+      </c>
+      <c r="J95" s="4">
+        <v>8</v>
+      </c>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="4">
         <v>27</v>
       </c>
-      <c r="N95" s="6">
+      <c r="N95" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A96" s="5">
+      <c r="A96" s="3">
         <v>3094</v>
       </c>
-      <c r="B96" s="5" t="s">
+      <c r="B96" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C96" s="5">
-        <v>32</v>
-      </c>
-      <c r="D96" s="5">
-        <v>8</v>
-      </c>
-      <c r="E96" s="6">
+      <c r="C96" s="3">
+        <v>32</v>
+      </c>
+      <c r="D96" s="3">
+        <v>8</v>
+      </c>
+      <c r="E96" s="4">
         <v>19</v>
       </c>
-      <c r="F96" s="6">
-        <v>7</v>
-      </c>
-      <c r="G96" s="6"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="6"/>
-      <c r="L96" s="6"/>
-      <c r="M96" s="6">
+      <c r="F96" s="4">
+        <v>7</v>
+      </c>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4">
+        <v>29</v>
+      </c>
+      <c r="J96" s="4">
+        <v>8</v>
+      </c>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="4">
         <v>27</v>
       </c>
-      <c r="N96" s="6">
+      <c r="N96" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="97" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A97" s="5">
+      <c r="A97" s="3">
         <v>3095</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B97" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C97" s="5">
-        <v>32</v>
-      </c>
-      <c r="D97" s="5">
-        <v>8</v>
-      </c>
-      <c r="E97" s="6">
+      <c r="C97" s="3">
+        <v>32</v>
+      </c>
+      <c r="D97" s="3">
+        <v>8</v>
+      </c>
+      <c r="E97" s="4">
         <v>30</v>
       </c>
-      <c r="F97" s="6">
+      <c r="F97" s="4">
         <v>9</v>
       </c>
-      <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6"/>
-      <c r="J97" s="6"/>
-      <c r="K97" s="6"/>
-      <c r="L97" s="6"/>
-      <c r="M97" s="6">
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4">
+        <v>36</v>
+      </c>
+      <c r="J97" s="4">
+        <v>10</v>
+      </c>
+      <c r="K97" s="4"/>
+      <c r="L97" s="4"/>
+      <c r="M97" s="4">
         <v>30</v>
       </c>
-      <c r="N97" s="6">
+      <c r="N97" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A98" s="5">
+      <c r="A98" s="3">
         <v>3096</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B98" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C98" s="5">
+      <c r="C98" s="3">
         <v>29</v>
       </c>
-      <c r="D98" s="5">
-        <v>7</v>
-      </c>
-      <c r="E98" s="6">
+      <c r="D98" s="3">
+        <v>7</v>
+      </c>
+      <c r="E98" s="4">
         <v>27</v>
       </c>
-      <c r="F98" s="6">
-        <v>8</v>
-      </c>
-      <c r="G98" s="6"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="6"/>
-      <c r="J98" s="6"/>
-      <c r="K98" s="6"/>
-      <c r="L98" s="6"/>
-      <c r="M98" s="6">
+      <c r="F98" s="4">
+        <v>8</v>
+      </c>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4">
+        <v>35</v>
+      </c>
+      <c r="J98" s="4">
+        <v>10</v>
+      </c>
+      <c r="K98" s="4"/>
+      <c r="L98" s="4"/>
+      <c r="M98" s="4">
         <v>27</v>
       </c>
-      <c r="N98" s="6">
+      <c r="N98" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A99" s="5">
+      <c r="A99" s="3">
         <v>3097</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C99" s="5">
-        <v>32</v>
-      </c>
-      <c r="D99" s="5">
-        <v>8</v>
-      </c>
-      <c r="E99" s="6">
+      <c r="C99" s="3">
+        <v>32</v>
+      </c>
+      <c r="D99" s="3">
+        <v>8</v>
+      </c>
+      <c r="E99" s="4">
         <v>33</v>
       </c>
-      <c r="F99" s="6">
+      <c r="F99" s="4">
         <v>4</v>
       </c>
-      <c r="G99" s="6"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6"/>
-      <c r="L99" s="6"/>
-      <c r="M99" s="6">
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4">
+        <v>32</v>
+      </c>
+      <c r="J99" s="4">
+        <v>8</v>
+      </c>
+      <c r="K99" s="4"/>
+      <c r="L99" s="4"/>
+      <c r="M99" s="4">
         <v>31</v>
       </c>
-      <c r="N99" s="6">
+      <c r="N99" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A100" s="5">
+      <c r="A100" s="3">
         <v>3098</v>
       </c>
-      <c r="B100" s="5" t="s">
+      <c r="B100" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C100" s="5">
+      <c r="C100" s="3">
         <v>29</v>
       </c>
-      <c r="D100" s="5">
-        <v>7</v>
-      </c>
-      <c r="E100" s="6">
+      <c r="D100" s="3">
+        <v>7</v>
+      </c>
+      <c r="E100" s="4">
         <v>35</v>
       </c>
-      <c r="F100" s="6">
+      <c r="F100" s="4">
         <v>9</v>
       </c>
-      <c r="G100" s="6"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="6"/>
-      <c r="L100" s="6"/>
-      <c r="M100" s="6">
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4">
+        <v>36</v>
+      </c>
+      <c r="J100" s="4">
+        <v>8</v>
+      </c>
+      <c r="K100" s="4"/>
+      <c r="L100" s="4"/>
+      <c r="M100" s="4">
         <v>37</v>
       </c>
-      <c r="N100" s="6">
+      <c r="N100" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A101" s="5">
+      <c r="A101" s="3">
         <v>3099</v>
       </c>
-      <c r="B101" s="5" t="s">
+      <c r="B101" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C101" s="5">
+      <c r="C101" s="3">
         <v>35</v>
       </c>
-      <c r="D101" s="5">
+      <c r="D101" s="3">
         <v>9</v>
       </c>
-      <c r="E101" s="6">
-        <v>32</v>
-      </c>
-      <c r="F101" s="6">
+      <c r="E101" s="4">
+        <v>32</v>
+      </c>
+      <c r="F101" s="4">
         <v>9</v>
       </c>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
-      <c r="J101" s="6"/>
-      <c r="K101" s="6"/>
-      <c r="L101" s="6"/>
-      <c r="M101" s="6">
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+      <c r="I101" s="4">
+        <v>36</v>
+      </c>
+      <c r="J101" s="4">
+        <v>10</v>
+      </c>
+      <c r="K101" s="4"/>
+      <c r="L101" s="4"/>
+      <c r="M101" s="4">
         <v>29</v>
       </c>
-      <c r="N101" s="6">
+      <c r="N101" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A102" s="5">
+      <c r="A102" s="3">
         <v>3100</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B102" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C102" s="5">
+      <c r="C102" s="3">
         <v>29</v>
       </c>
-      <c r="D102" s="5">
-        <v>7</v>
-      </c>
-      <c r="E102" s="6">
+      <c r="D102" s="3">
+        <v>7</v>
+      </c>
+      <c r="E102" s="4">
         <v>28</v>
       </c>
-      <c r="F102" s="6">
-        <v>7</v>
-      </c>
-      <c r="G102" s="6"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6"/>
-      <c r="J102" s="6"/>
-      <c r="K102" s="6"/>
-      <c r="L102" s="6"/>
-      <c r="M102" s="6">
+      <c r="F102" s="4">
+        <v>7</v>
+      </c>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4">
+        <v>31</v>
+      </c>
+      <c r="J102" s="4">
+        <v>9</v>
+      </c>
+      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4">
         <v>25</v>
       </c>
-      <c r="N102" s="6">
+      <c r="N102" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="103" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A103" s="5">
+      <c r="A103" s="3">
         <v>3101</v>
       </c>
-      <c r="B103" s="5" t="s">
+      <c r="B103" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C103" s="5">
+      <c r="C103" s="3">
         <v>38</v>
       </c>
-      <c r="D103" s="5">
-        <v>10</v>
-      </c>
-      <c r="E103" s="6">
+      <c r="D103" s="3">
+        <v>10</v>
+      </c>
+      <c r="E103" s="4">
         <v>37</v>
       </c>
-      <c r="F103" s="6">
+      <c r="F103" s="4">
         <v>9</v>
       </c>
-      <c r="G103" s="6"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="6"/>
-      <c r="J103" s="6"/>
-      <c r="K103" s="6"/>
-      <c r="L103" s="6"/>
-      <c r="M103" s="6">
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4">
+        <v>37</v>
+      </c>
+      <c r="J103" s="4">
+        <v>10</v>
+      </c>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4">
         <v>36</v>
       </c>
-      <c r="N103" s="6">
+      <c r="N103" s="4">
         <v>9</v>
       </c>
     </row>
     <row r="104" spans="1:14" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A104" s="5">
+      <c r="A104" s="3">
         <v>3102</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B104" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C104" s="5">
+      <c r="C104" s="3">
         <v>38</v>
       </c>
-      <c r="D104" s="5">
-        <v>10</v>
-      </c>
-      <c r="E104" s="6">
+      <c r="D104" s="3">
+        <v>10</v>
+      </c>
+      <c r="E104" s="4">
         <v>36</v>
       </c>
-      <c r="F104" s="6">
-        <v>8</v>
-      </c>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6"/>
-      <c r="J104" s="6"/>
-      <c r="K104" s="6"/>
-      <c r="L104" s="6"/>
-      <c r="M104" s="6">
+      <c r="F104" s="4">
+        <v>8</v>
+      </c>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4"/>
+      <c r="I104" s="4">
+        <v>36</v>
+      </c>
+      <c r="J104" s="4">
+        <v>10</v>
+      </c>
+      <c r="K104" s="4"/>
+      <c r="L104" s="4"/>
+      <c r="M104" s="4">
         <v>34</v>
       </c>
-      <c r="N104" s="6">
+      <c r="N104" s="4">
         <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A105" s="7"/>
-      <c r="B105" s="7"/>
-      <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
-      <c r="F105" s="8"/>
-      <c r="G105" s="8"/>
-      <c r="H105" s="8"/>
-      <c r="I105" s="8"/>
-      <c r="J105" s="8"/>
+      <c r="A105" s="5"/>
+      <c r="B105" s="5"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
+      <c r="I105" s="6"/>
+      <c r="J105" s="6"/>
     </row>
     <row r="106" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A106" s="7"/>
-      <c r="B106" s="7"/>
-      <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="8"/>
-      <c r="G106" s="8"/>
-      <c r="H106" s="8"/>
-      <c r="I106" s="8"/>
-      <c r="J106" s="8"/>
+      <c r="A106" s="5"/>
+      <c r="B106" s="5"/>
+      <c r="C106" s="6"/>
+      <c r="D106" s="6"/>
+      <c r="E106" s="6"/>
+      <c r="F106" s="6"/>
+      <c r="G106" s="6"/>
+      <c r="H106" s="6"/>
+      <c r="I106" s="6"/>
+      <c r="J106" s="6"/>
     </row>
     <row r="107" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A107" s="7"/>
-      <c r="B107" s="7"/>
-      <c r="C107" s="8"/>
-      <c r="D107" s="8"/>
-      <c r="E107" s="8"/>
-      <c r="F107" s="8"/>
-      <c r="G107" s="8"/>
-      <c r="H107" s="8"/>
-      <c r="I107" s="8"/>
-      <c r="J107" s="8"/>
+      <c r="A107" s="5"/>
+      <c r="B107" s="5"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="6"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="6"/>
+      <c r="G107" s="6"/>
+      <c r="H107" s="6"/>
+      <c r="I107" s="6"/>
+      <c r="J107" s="6"/>
     </row>
     <row r="108" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A108" s="7"/>
-      <c r="B108" s="7"/>
-      <c r="C108" s="8"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="8"/>
-      <c r="F108" s="8"/>
-      <c r="G108" s="8"/>
-      <c r="H108" s="8"/>
-      <c r="I108" s="8"/>
-      <c r="J108" s="8"/>
+      <c r="A108" s="5"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="6"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="6"/>
+      <c r="H108" s="6"/>
+      <c r="I108" s="6"/>
+      <c r="J108" s="6"/>
     </row>
     <row r="109" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A109" s="7"/>
-      <c r="B109" s="7"/>
-      <c r="C109" s="8"/>
-      <c r="D109" s="8"/>
-      <c r="E109" s="8"/>
-      <c r="F109" s="8"/>
-      <c r="G109" s="8"/>
-      <c r="H109" s="8"/>
-      <c r="I109" s="8"/>
-      <c r="J109" s="8"/>
+      <c r="A109" s="5"/>
+      <c r="B109" s="5"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="6"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="6"/>
+      <c r="G109" s="6"/>
+      <c r="H109" s="6"/>
+      <c r="I109" s="6"/>
+      <c r="J109" s="6"/>
     </row>
     <row r="110" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A110" s="7"/>
-      <c r="B110" s="7"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="8"/>
-      <c r="G110" s="8"/>
-      <c r="H110" s="8"/>
-      <c r="I110" s="8"/>
-      <c r="J110" s="8"/>
+      <c r="A110" s="5"/>
+      <c r="B110" s="5"/>
+      <c r="C110" s="6"/>
+      <c r="D110" s="6"/>
+      <c r="E110" s="6"/>
+      <c r="F110" s="6"/>
+      <c r="G110" s="6"/>
+      <c r="H110" s="6"/>
+      <c r="I110" s="6"/>
+      <c r="J110" s="6"/>
     </row>
     <row r="111" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A111" s="7"/>
-      <c r="B111" s="7"/>
-      <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="8"/>
-      <c r="G111" s="8"/>
-      <c r="H111" s="8"/>
-      <c r="I111" s="8"/>
-      <c r="J111" s="8"/>
+      <c r="A111" s="5"/>
+      <c r="B111" s="5"/>
+      <c r="C111" s="6"/>
+      <c r="D111" s="6"/>
+      <c r="E111" s="6"/>
+      <c r="F111" s="6"/>
+      <c r="G111" s="6"/>
+      <c r="H111" s="6"/>
+      <c r="I111" s="6"/>
+      <c r="J111" s="6"/>
     </row>
     <row r="112" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A112" s="7"/>
-      <c r="B112" s="7"/>
-      <c r="C112" s="8"/>
-      <c r="D112" s="8"/>
-      <c r="E112" s="8"/>
-      <c r="F112" s="8"/>
-      <c r="G112" s="8"/>
-      <c r="H112" s="8"/>
-      <c r="I112" s="8"/>
-      <c r="J112" s="8"/>
+      <c r="A112" s="5"/>
+      <c r="B112" s="5"/>
+      <c r="C112" s="6"/>
+      <c r="D112" s="6"/>
+      <c r="E112" s="6"/>
+      <c r="F112" s="6"/>
+      <c r="G112" s="6"/>
+      <c r="H112" s="6"/>
+      <c r="I112" s="6"/>
+      <c r="J112" s="6"/>
     </row>
     <row r="113" spans="1:10" ht="21" x14ac:dyDescent="0.4">
-      <c r="A113" s="7"/>
-      <c r="B113" s="7"/>
-      <c r="C113" s="8"/>
-      <c r="D113" s="8"/>
-      <c r="E113" s="8"/>
-      <c r="F113" s="8"/>
-      <c r="G113" s="8"/>
-      <c r="H113" s="8"/>
-      <c r="I113" s="8"/>
-      <c r="J113" s="8"/>
+      <c r="A113" s="5"/>
+      <c r="B113" s="5"/>
+      <c r="C113" s="6"/>
+      <c r="D113" s="6"/>
+      <c r="E113" s="6"/>
+      <c r="F113" s="6"/>
+      <c r="G113" s="6"/>
+      <c r="H113" s="6"/>
+      <c r="I113" s="6"/>
+      <c r="J113" s="6"/>
     </row>
     <row r="114" spans="1:10" ht="21" x14ac:dyDescent="0.4">
-      <c r="A114" s="7"/>
-      <c r="B114" s="7"/>
-      <c r="C114" s="8"/>
-      <c r="D114" s="8"/>
-      <c r="E114" s="8"/>
-      <c r="F114" s="8"/>
-      <c r="G114" s="8"/>
-      <c r="H114" s="8"/>
-      <c r="I114" s="8"/>
-      <c r="J114" s="8"/>
+      <c r="A114" s="5"/>
+      <c r="B114" s="5"/>
+      <c r="C114" s="6"/>
+      <c r="D114" s="6"/>
+      <c r="E114" s="6"/>
+      <c r="F114" s="6"/>
+      <c r="G114" s="6"/>
+      <c r="H114" s="6"/>
+      <c r="I114" s="6"/>
+      <c r="J114" s="6"/>
     </row>
     <row r="115" spans="1:10" ht="21" x14ac:dyDescent="0.4">
-      <c r="A115" s="7"/>
-      <c r="B115" s="7"/>
-      <c r="C115" s="8"/>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
-      <c r="F115" s="8"/>
-      <c r="G115" s="8"/>
-      <c r="H115" s="8"/>
-      <c r="I115" s="8"/>
-      <c r="J115" s="8"/>
+      <c r="A115" s="5"/>
+      <c r="B115" s="5"/>
+      <c r="C115" s="6"/>
+      <c r="D115" s="6"/>
+      <c r="E115" s="6"/>
+      <c r="F115" s="6"/>
+      <c r="G115" s="6"/>
+      <c r="H115" s="6"/>
+      <c r="I115" s="6"/>
+      <c r="J115" s="6"/>
     </row>
     <row r="116" spans="1:10" ht="21" x14ac:dyDescent="0.4">
-      <c r="A116" s="7"/>
-      <c r="B116" s="7"/>
-      <c r="C116" s="8"/>
-      <c r="D116" s="8"/>
-      <c r="E116" s="8"/>
-      <c r="F116" s="8"/>
-      <c r="G116" s="8"/>
-      <c r="H116" s="8"/>
-      <c r="I116" s="8"/>
-      <c r="J116" s="8"/>
+      <c r="A116" s="5"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="6"/>
+      <c r="D116" s="6"/>
+      <c r="E116" s="6"/>
+      <c r="F116" s="6"/>
+      <c r="G116" s="6"/>
+      <c r="H116" s="6"/>
+      <c r="I116" s="6"/>
+      <c r="J116" s="6"/>
     </row>
     <row r="117" spans="1:10" ht="21" x14ac:dyDescent="0.4">
-      <c r="A117" s="7"/>
-      <c r="B117" s="7"/>
-      <c r="C117" s="8"/>
-      <c r="D117" s="8"/>
-      <c r="E117" s="8"/>
-      <c r="F117" s="8"/>
-      <c r="G117" s="8"/>
-      <c r="H117" s="8"/>
-      <c r="I117" s="8"/>
-      <c r="J117" s="8"/>
+      <c r="A117" s="5"/>
+      <c r="B117" s="5"/>
+      <c r="C117" s="6"/>
+      <c r="D117" s="6"/>
+      <c r="E117" s="6"/>
+      <c r="F117" s="6"/>
+      <c r="G117" s="6"/>
+      <c r="H117" s="6"/>
+      <c r="I117" s="6"/>
+      <c r="J117" s="6"/>
     </row>
     <row r="118" spans="1:10" ht="21" x14ac:dyDescent="0.4">
-      <c r="A118" s="7"/>
-      <c r="B118" s="7"/>
-      <c r="C118" s="8"/>
-      <c r="D118" s="8"/>
-      <c r="E118" s="8"/>
-      <c r="F118" s="8"/>
-      <c r="G118" s="8"/>
-      <c r="H118" s="8"/>
-      <c r="I118" s="8"/>
-      <c r="J118" s="8"/>
+      <c r="A118" s="5"/>
+      <c r="B118" s="5"/>
+      <c r="C118" s="6"/>
+      <c r="D118" s="6"/>
+      <c r="E118" s="6"/>
+      <c r="F118" s="6"/>
+      <c r="G118" s="6"/>
+      <c r="H118" s="6"/>
+      <c r="I118" s="6"/>
+      <c r="J118" s="6"/>
     </row>
     <row r="119" spans="1:10" ht="21" x14ac:dyDescent="0.4">
-      <c r="A119" s="7"/>
-      <c r="B119" s="7"/>
-      <c r="C119" s="8"/>
-      <c r="D119" s="8"/>
-      <c r="E119" s="8"/>
-      <c r="F119" s="8"/>
-      <c r="G119" s="8"/>
-      <c r="H119" s="8"/>
-      <c r="I119" s="8"/>
-      <c r="J119" s="8"/>
+      <c r="A119" s="5"/>
+      <c r="B119" s="5"/>
+      <c r="C119" s="6"/>
+      <c r="D119" s="6"/>
+      <c r="E119" s="6"/>
+      <c r="F119" s="6"/>
+      <c r="G119" s="6"/>
+      <c r="H119" s="6"/>
+      <c r="I119" s="6"/>
+      <c r="J119" s="6"/>
     </row>
     <row r="120" spans="1:10" ht="21" x14ac:dyDescent="0.4">
-      <c r="A120" s="7"/>
-      <c r="B120" s="7"/>
-      <c r="C120" s="8"/>
-      <c r="D120" s="8"/>
-      <c r="E120" s="8"/>
-      <c r="F120" s="8"/>
-      <c r="G120" s="8"/>
-      <c r="H120" s="8"/>
-      <c r="I120" s="8"/>
-      <c r="J120" s="8"/>
+      <c r="A120" s="5"/>
+      <c r="B120" s="5"/>
+      <c r="C120" s="6"/>
+      <c r="D120" s="6"/>
+      <c r="E120" s="6"/>
+      <c r="F120" s="6"/>
+      <c r="G120" s="6"/>
+      <c r="H120" s="6"/>
+      <c r="I120" s="6"/>
+      <c r="J120" s="6"/>
     </row>
     <row r="121" spans="1:10" ht="21" x14ac:dyDescent="0.4">
-      <c r="A121" s="7"/>
-      <c r="B121" s="7"/>
-      <c r="C121" s="8"/>
-      <c r="D121" s="8"/>
-      <c r="E121" s="8"/>
-      <c r="F121" s="8"/>
-      <c r="G121" s="8"/>
-      <c r="H121" s="8"/>
-      <c r="I121" s="8"/>
-      <c r="J121" s="8"/>
+      <c r="A121" s="5"/>
+      <c r="B121" s="5"/>
+      <c r="C121" s="6"/>
+      <c r="D121" s="6"/>
+      <c r="E121" s="6"/>
+      <c r="F121" s="6"/>
+      <c r="G121" s="6"/>
+      <c r="H121" s="6"/>
+      <c r="I121" s="6"/>
+      <c r="J121" s="6"/>
     </row>
     <row r="122" spans="1:10" ht="21" x14ac:dyDescent="0.4">
-      <c r="A122" s="7"/>
-      <c r="B122" s="7"/>
-      <c r="C122" s="8"/>
-      <c r="D122" s="8"/>
-      <c r="E122" s="8"/>
-      <c r="F122" s="8"/>
-      <c r="G122" s="8"/>
-      <c r="H122" s="8"/>
-      <c r="I122" s="8"/>
-      <c r="J122" s="8"/>
+      <c r="A122" s="5"/>
+      <c r="B122" s="5"/>
+      <c r="C122" s="6"/>
+      <c r="D122" s="6"/>
+      <c r="E122" s="6"/>
+      <c r="F122" s="6"/>
+      <c r="G122" s="6"/>
+      <c r="H122" s="6"/>
+      <c r="I122" s="6"/>
+      <c r="J122" s="6"/>
     </row>
     <row r="123" spans="1:10" ht="21" x14ac:dyDescent="0.4">
-      <c r="A123" s="7"/>
-      <c r="B123" s="7"/>
-      <c r="C123" s="8"/>
-      <c r="D123" s="8"/>
-      <c r="E123" s="8"/>
-      <c r="F123" s="8"/>
-      <c r="G123" s="8"/>
-      <c r="H123" s="8"/>
-      <c r="I123" s="8"/>
-      <c r="J123" s="8"/>
+      <c r="A123" s="5"/>
+      <c r="B123" s="5"/>
+      <c r="C123" s="6"/>
+      <c r="D123" s="6"/>
+      <c r="E123" s="6"/>
+      <c r="F123" s="6"/>
+      <c r="G123" s="6"/>
+      <c r="H123" s="6"/>
+      <c r="I123" s="6"/>
+      <c r="J123" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/m3.xlsx
+++ b/m3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\سعيات\م2 - ف2\steam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A579449-124C-4C7A-89F4-5709A6B2DD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B386E296-F48E-4726-8983-6699C850318A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -881,8 +881,12 @@
       <c r="F3" s="4">
         <v>8</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="G3" s="4">
+        <v>33</v>
+      </c>
+      <c r="H3" s="4">
+        <v>10</v>
+      </c>
       <c r="I3" s="4">
         <v>35</v>
       </c>
@@ -917,8 +921,12 @@
       <c r="F4" s="4">
         <v>7</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="G4" s="4">
+        <v>32</v>
+      </c>
+      <c r="H4" s="4">
+        <v>8</v>
+      </c>
       <c r="I4" s="4">
         <v>33</v>
       </c>
@@ -953,8 +961,12 @@
       <c r="F5" s="4">
         <v>6</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="G5" s="4">
+        <v>26</v>
+      </c>
+      <c r="H5" s="4">
+        <v>5</v>
+      </c>
       <c r="I5" s="4">
         <v>26</v>
       </c>
@@ -989,8 +1001,12 @@
       <c r="F6" s="4">
         <v>6</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="G6" s="4">
+        <v>33</v>
+      </c>
+      <c r="H6" s="4">
+        <v>9</v>
+      </c>
       <c r="I6" s="4">
         <v>27</v>
       </c>
@@ -1025,8 +1041,12 @@
       <c r="F7" s="4">
         <v>4</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="G7" s="4">
+        <v>36</v>
+      </c>
+      <c r="H7" s="4">
+        <v>9</v>
+      </c>
       <c r="I7" s="4">
         <v>30</v>
       </c>
@@ -1061,8 +1081,12 @@
       <c r="F8" s="4">
         <v>10</v>
       </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="G8" s="4">
+        <v>40</v>
+      </c>
+      <c r="H8" s="4">
+        <v>10</v>
+      </c>
       <c r="I8" s="4">
         <v>40</v>
       </c>
@@ -1097,8 +1121,12 @@
       <c r="F9" s="4">
         <v>4</v>
       </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="G9" s="4">
+        <v>30</v>
+      </c>
+      <c r="H9" s="4">
+        <v>7</v>
+      </c>
       <c r="I9" s="4">
         <v>29</v>
       </c>
@@ -1133,8 +1161,12 @@
       <c r="F10" s="4">
         <v>5</v>
       </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="G10" s="4">
+        <v>31</v>
+      </c>
+      <c r="H10" s="4">
+        <v>8</v>
+      </c>
       <c r="I10" s="4">
         <v>28</v>
       </c>
@@ -1169,8 +1201,12 @@
       <c r="F11" s="4">
         <v>8</v>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="G11" s="4">
+        <v>31</v>
+      </c>
+      <c r="H11" s="4">
+        <v>8</v>
+      </c>
       <c r="I11" s="4">
         <v>36</v>
       </c>
@@ -1205,8 +1241,12 @@
       <c r="F12" s="4">
         <v>10</v>
       </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="G12" s="4">
+        <v>40</v>
+      </c>
+      <c r="H12" s="4">
+        <v>10</v>
+      </c>
       <c r="I12" s="4">
         <v>40</v>
       </c>
@@ -1241,8 +1281,12 @@
       <c r="F13" s="4">
         <v>9</v>
       </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="G13" s="4">
+        <v>38</v>
+      </c>
+      <c r="H13" s="4">
+        <v>10</v>
+      </c>
       <c r="I13" s="4">
         <v>38</v>
       </c>
@@ -1277,8 +1321,12 @@
       <c r="F14" s="4">
         <v>4</v>
       </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="G14" s="4">
+        <v>38</v>
+      </c>
+      <c r="H14" s="4">
+        <v>10</v>
+      </c>
       <c r="I14" s="4">
         <v>40</v>
       </c>
@@ -1313,8 +1361,12 @@
       <c r="F15" s="4">
         <v>0</v>
       </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="G15" s="4">
+        <v>27</v>
+      </c>
+      <c r="H15" s="4">
+        <v>5</v>
+      </c>
       <c r="I15" s="4">
         <v>31</v>
       </c>
@@ -1349,8 +1401,12 @@
       <c r="F16" s="4">
         <v>7</v>
       </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="G16" s="4">
+        <v>37</v>
+      </c>
+      <c r="H16" s="4">
+        <v>10</v>
+      </c>
       <c r="I16" s="4">
         <v>37</v>
       </c>
@@ -1385,8 +1441,12 @@
       <c r="F17" s="4">
         <v>8</v>
       </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="G17" s="4">
+        <v>37</v>
+      </c>
+      <c r="H17" s="4">
+        <v>10</v>
+      </c>
       <c r="I17" s="4">
         <v>32</v>
       </c>
@@ -1421,8 +1481,12 @@
       <c r="F18" s="4">
         <v>5</v>
       </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
+      <c r="G18" s="4">
+        <v>29</v>
+      </c>
+      <c r="H18" s="4">
+        <v>6</v>
+      </c>
       <c r="I18" s="4">
         <v>29</v>
       </c>
@@ -1457,8 +1521,12 @@
       <c r="F19" s="4">
         <v>4</v>
       </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="G19" s="4">
+        <v>34</v>
+      </c>
+      <c r="H19" s="4">
+        <v>10</v>
+      </c>
       <c r="I19" s="4">
         <v>32</v>
       </c>
@@ -1493,8 +1561,12 @@
       <c r="F20" s="4">
         <v>7</v>
       </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="G20" s="4">
+        <v>36</v>
+      </c>
+      <c r="H20" s="4">
+        <v>9</v>
+      </c>
       <c r="I20" s="4">
         <v>34</v>
       </c>
@@ -1529,8 +1601,12 @@
       <c r="F21" s="4">
         <v>6</v>
       </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="G21" s="4">
+        <v>35</v>
+      </c>
+      <c r="H21" s="4">
+        <v>9</v>
+      </c>
       <c r="I21" s="4">
         <v>33</v>
       </c>
@@ -1565,8 +1641,12 @@
       <c r="F22" s="4">
         <v>5</v>
       </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="G22" s="4">
+        <v>36</v>
+      </c>
+      <c r="H22" s="4">
+        <v>6</v>
+      </c>
       <c r="I22" s="4">
         <v>32</v>
       </c>
@@ -1601,8 +1681,12 @@
       <c r="F23" s="4">
         <v>4</v>
       </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
+      <c r="G23" s="4">
+        <v>29</v>
+      </c>
+      <c r="H23" s="4">
+        <v>8</v>
+      </c>
       <c r="I23" s="4">
         <v>32</v>
       </c>
@@ -1637,8 +1721,12 @@
       <c r="F24" s="4">
         <v>8</v>
       </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
+      <c r="G24" s="4">
+        <v>27</v>
+      </c>
+      <c r="H24" s="4">
+        <v>9</v>
+      </c>
       <c r="I24" s="4">
         <v>31</v>
       </c>
@@ -1673,8 +1761,12 @@
       <c r="F25" s="4">
         <v>6</v>
       </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
+      <c r="G25" s="4">
+        <v>28</v>
+      </c>
+      <c r="H25" s="4">
+        <v>5</v>
+      </c>
       <c r="I25" s="4">
         <v>35</v>
       </c>
@@ -1709,8 +1801,12 @@
       <c r="F26" s="4">
         <v>9</v>
       </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
+      <c r="G26" s="4">
+        <v>40</v>
+      </c>
+      <c r="H26" s="4">
+        <v>10</v>
+      </c>
       <c r="I26" s="4">
         <v>40</v>
       </c>
@@ -1745,8 +1841,12 @@
       <c r="F27" s="4">
         <v>6</v>
       </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
+      <c r="G27" s="4">
+        <v>32</v>
+      </c>
+      <c r="H27" s="4">
+        <v>8</v>
+      </c>
       <c r="I27" s="4">
         <v>27</v>
       </c>
@@ -1781,8 +1881,12 @@
       <c r="F28" s="4">
         <v>5</v>
       </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
+      <c r="G28" s="4">
+        <v>28</v>
+      </c>
+      <c r="H28" s="4">
+        <v>7</v>
+      </c>
       <c r="I28" s="4">
         <v>34</v>
       </c>
@@ -1817,8 +1921,12 @@
       <c r="F29" s="4">
         <v>3</v>
       </c>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
+      <c r="G29" s="4">
+        <v>36</v>
+      </c>
+      <c r="H29" s="4">
+        <v>9</v>
+      </c>
       <c r="I29" s="4">
         <v>30</v>
       </c>
@@ -1853,8 +1961,12 @@
       <c r="F30" s="4">
         <v>5</v>
       </c>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="G30" s="4">
+        <v>30</v>
+      </c>
+      <c r="H30" s="4">
+        <v>10</v>
+      </c>
       <c r="I30" s="4">
         <v>34</v>
       </c>
@@ -1889,8 +2001,12 @@
       <c r="F31" s="4">
         <v>6</v>
       </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
+      <c r="G31" s="4">
+        <v>38</v>
+      </c>
+      <c r="H31" s="4">
+        <v>10</v>
+      </c>
       <c r="I31" s="4">
         <v>36</v>
       </c>
@@ -1925,8 +2041,12 @@
       <c r="F32" s="4">
         <v>9</v>
       </c>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
+      <c r="G32" s="4">
+        <v>38</v>
+      </c>
+      <c r="H32" s="4">
+        <v>10</v>
+      </c>
       <c r="I32" s="4">
         <v>38</v>
       </c>
@@ -1961,8 +2081,12 @@
       <c r="F33" s="4">
         <v>8</v>
       </c>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
+      <c r="G33" s="4">
+        <v>39</v>
+      </c>
+      <c r="H33" s="4">
+        <v>10</v>
+      </c>
       <c r="I33" s="4">
         <v>34</v>
       </c>
@@ -1997,8 +2121,12 @@
       <c r="F34" s="4">
         <v>8</v>
       </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
+      <c r="G34" s="4">
+        <v>33</v>
+      </c>
+      <c r="H34" s="4">
+        <v>10</v>
+      </c>
       <c r="I34" s="4">
         <v>35</v>
       </c>
@@ -2033,8 +2161,12 @@
       <c r="F35" s="4">
         <v>8</v>
       </c>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
+      <c r="G35" s="4">
+        <v>38</v>
+      </c>
+      <c r="H35" s="4">
+        <v>9</v>
+      </c>
       <c r="I35" s="4">
         <v>39</v>
       </c>
@@ -2069,8 +2201,12 @@
       <c r="F36" s="4">
         <v>5</v>
       </c>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
+      <c r="G36" s="4">
+        <v>39</v>
+      </c>
+      <c r="H36" s="4">
+        <v>10</v>
+      </c>
       <c r="I36" s="4">
         <v>38</v>
       </c>
@@ -2105,8 +2241,12 @@
       <c r="F37" s="4">
         <v>10</v>
       </c>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
+      <c r="G37" s="4">
+        <v>40</v>
+      </c>
+      <c r="H37" s="4">
+        <v>10</v>
+      </c>
       <c r="I37" s="4">
         <v>40</v>
       </c>
@@ -2141,8 +2281,12 @@
       <c r="F38" s="4">
         <v>9</v>
       </c>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
+      <c r="G38" s="4">
+        <v>33</v>
+      </c>
+      <c r="H38" s="4">
+        <v>10</v>
+      </c>
       <c r="I38" s="4">
         <v>36</v>
       </c>
@@ -2177,8 +2321,12 @@
       <c r="F39" s="4">
         <v>6</v>
       </c>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
+      <c r="G39" s="4">
+        <v>37</v>
+      </c>
+      <c r="H39" s="4">
+        <v>10</v>
+      </c>
       <c r="I39" s="4">
         <v>27</v>
       </c>
@@ -2213,8 +2361,12 @@
       <c r="F40" s="4">
         <v>8</v>
       </c>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
+      <c r="G40" s="4">
+        <v>31</v>
+      </c>
+      <c r="H40" s="4">
+        <v>10</v>
+      </c>
       <c r="I40" s="4">
         <v>31</v>
       </c>
@@ -2249,8 +2401,12 @@
       <c r="F41" s="4">
         <v>7</v>
       </c>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
+      <c r="G41" s="4">
+        <v>38</v>
+      </c>
+      <c r="H41" s="4">
+        <v>10</v>
+      </c>
       <c r="I41" s="4">
         <v>35</v>
       </c>
@@ -2285,8 +2441,12 @@
       <c r="F42" s="4">
         <v>6</v>
       </c>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
+      <c r="G42" s="4">
+        <v>34</v>
+      </c>
+      <c r="H42" s="4">
+        <v>9</v>
+      </c>
       <c r="I42" s="4">
         <v>31</v>
       </c>
@@ -2321,8 +2481,12 @@
       <c r="F43" s="4">
         <v>6</v>
       </c>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
+      <c r="G43" s="4">
+        <v>35</v>
+      </c>
+      <c r="H43" s="4">
+        <v>7</v>
+      </c>
       <c r="I43" s="4">
         <v>34</v>
       </c>
@@ -2357,8 +2521,12 @@
       <c r="F44" s="4">
         <v>8</v>
       </c>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
+      <c r="G44" s="4">
+        <v>40</v>
+      </c>
+      <c r="H44" s="4">
+        <v>10</v>
+      </c>
       <c r="I44" s="4">
         <v>37</v>
       </c>
@@ -2393,8 +2561,12 @@
       <c r="F45" s="4">
         <v>0</v>
       </c>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
+      <c r="G45" s="4">
+        <v>35</v>
+      </c>
+      <c r="H45" s="4">
+        <v>9</v>
+      </c>
       <c r="I45" s="4">
         <v>36</v>
       </c>
@@ -2429,8 +2601,12 @@
       <c r="F46" s="4">
         <v>7</v>
       </c>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
+      <c r="G46" s="4">
+        <v>38</v>
+      </c>
+      <c r="H46" s="4">
+        <v>10</v>
+      </c>
       <c r="I46" s="4">
         <v>39</v>
       </c>
@@ -2465,8 +2641,12 @@
       <c r="F47" s="4">
         <v>6</v>
       </c>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
+      <c r="G47" s="4">
+        <v>39</v>
+      </c>
+      <c r="H47" s="4">
+        <v>10</v>
+      </c>
       <c r="I47" s="4">
         <v>34</v>
       </c>
@@ -2501,8 +2681,12 @@
       <c r="F48" s="4">
         <v>0</v>
       </c>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
+      <c r="G48" s="4">
+        <v>29</v>
+      </c>
+      <c r="H48" s="4">
+        <v>7</v>
+      </c>
       <c r="I48" s="4">
         <v>32</v>
       </c>
@@ -2537,8 +2721,12 @@
       <c r="F49" s="4">
         <v>4</v>
       </c>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
+      <c r="G49" s="4">
+        <v>36</v>
+      </c>
+      <c r="H49" s="4">
+        <v>9</v>
+      </c>
       <c r="I49" s="4">
         <v>29</v>
       </c>
@@ -2573,8 +2761,12 @@
       <c r="F50" s="4">
         <v>9</v>
       </c>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
+      <c r="G50" s="4">
+        <v>29</v>
+      </c>
+      <c r="H50" s="4">
+        <v>7</v>
+      </c>
       <c r="I50" s="4">
         <v>29</v>
       </c>
@@ -2609,8 +2801,12 @@
       <c r="F51" s="4">
         <v>4</v>
       </c>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
+      <c r="G51" s="4">
+        <v>35</v>
+      </c>
+      <c r="H51" s="4">
+        <v>6</v>
+      </c>
       <c r="I51" s="4">
         <v>29</v>
       </c>
@@ -2645,8 +2841,12 @@
       <c r="F52" s="4">
         <v>7</v>
       </c>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
+      <c r="G52" s="4">
+        <v>39</v>
+      </c>
+      <c r="H52" s="4">
+        <v>9</v>
+      </c>
       <c r="I52" s="4">
         <v>33</v>
       </c>
@@ -2681,8 +2881,12 @@
       <c r="F53" s="4">
         <v>4</v>
       </c>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
+      <c r="G53" s="4">
+        <v>27</v>
+      </c>
+      <c r="H53" s="4">
+        <v>6</v>
+      </c>
       <c r="I53" s="4">
         <v>24</v>
       </c>
@@ -2717,8 +2921,12 @@
       <c r="F54" s="4">
         <v>7</v>
       </c>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
+      <c r="G54" s="4">
+        <v>34</v>
+      </c>
+      <c r="H54" s="4">
+        <v>8</v>
+      </c>
       <c r="I54" s="4">
         <v>29</v>
       </c>
@@ -2753,8 +2961,12 @@
       <c r="F55" s="4">
         <v>6</v>
       </c>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
+      <c r="G55" s="4">
+        <v>32</v>
+      </c>
+      <c r="H55" s="4">
+        <v>10</v>
+      </c>
       <c r="I55" s="4">
         <v>35</v>
       </c>
@@ -2789,8 +3001,12 @@
       <c r="F56" s="4">
         <v>8</v>
       </c>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
+      <c r="G56" s="4">
+        <v>28</v>
+      </c>
+      <c r="H56" s="4">
+        <v>7</v>
+      </c>
       <c r="I56" s="4">
         <v>30</v>
       </c>
@@ -2825,8 +3041,12 @@
       <c r="F57" s="4">
         <v>8</v>
       </c>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
+      <c r="G57" s="4">
+        <v>40</v>
+      </c>
+      <c r="H57" s="4">
+        <v>10</v>
+      </c>
       <c r="I57" s="4">
         <v>40</v>
       </c>
@@ -2861,8 +3081,12 @@
       <c r="F58" s="4">
         <v>7</v>
       </c>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
+      <c r="G58" s="4">
+        <v>35</v>
+      </c>
+      <c r="H58" s="4">
+        <v>9</v>
+      </c>
       <c r="I58" s="4">
         <v>32</v>
       </c>
@@ -2897,8 +3121,12 @@
       <c r="F59" s="4">
         <v>8</v>
       </c>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
+      <c r="G59" s="4">
+        <v>40</v>
+      </c>
+      <c r="H59" s="4">
+        <v>10</v>
+      </c>
       <c r="I59" s="4">
         <v>40</v>
       </c>
@@ -2933,8 +3161,12 @@
       <c r="F60" s="4">
         <v>7</v>
       </c>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
+      <c r="G60" s="4">
+        <v>38</v>
+      </c>
+      <c r="H60" s="4">
+        <v>8</v>
+      </c>
       <c r="I60" s="4">
         <v>34</v>
       </c>
@@ -2969,8 +3201,12 @@
       <c r="F61" s="4">
         <v>7</v>
       </c>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
+      <c r="G61" s="4">
+        <v>37</v>
+      </c>
+      <c r="H61" s="4">
+        <v>7</v>
+      </c>
       <c r="I61" s="4">
         <v>32</v>
       </c>
@@ -3005,8 +3241,12 @@
       <c r="F62" s="4">
         <v>6</v>
       </c>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
+      <c r="G62" s="4">
+        <v>32</v>
+      </c>
+      <c r="H62" s="4">
+        <v>10</v>
+      </c>
       <c r="I62" s="4">
         <v>26</v>
       </c>
@@ -3041,8 +3281,12 @@
       <c r="F63" s="4">
         <v>6</v>
       </c>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
+      <c r="G63" s="4">
+        <v>37</v>
+      </c>
+      <c r="H63" s="4">
+        <v>7</v>
+      </c>
       <c r="I63" s="4">
         <v>30</v>
       </c>
@@ -3077,8 +3321,12 @@
       <c r="F64" s="4">
         <v>5</v>
       </c>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
+      <c r="G64" s="4">
+        <v>35</v>
+      </c>
+      <c r="H64" s="4">
+        <v>10</v>
+      </c>
       <c r="I64" s="4">
         <v>30</v>
       </c>
@@ -3113,8 +3361,12 @@
       <c r="F65" s="4">
         <v>5</v>
       </c>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
+      <c r="G65" s="4">
+        <v>29</v>
+      </c>
+      <c r="H65" s="4">
+        <v>6</v>
+      </c>
       <c r="I65" s="4">
         <v>28</v>
       </c>
@@ -3149,8 +3401,12 @@
       <c r="F66" s="4">
         <v>6</v>
       </c>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
+      <c r="G66" s="4">
+        <v>37</v>
+      </c>
+      <c r="H66" s="4">
+        <v>9</v>
+      </c>
       <c r="I66" s="4">
         <v>34</v>
       </c>
@@ -3185,8 +3441,12 @@
       <c r="F67" s="4">
         <v>9</v>
       </c>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
+      <c r="G67" s="4">
+        <v>37</v>
+      </c>
+      <c r="H67" s="4">
+        <v>10</v>
+      </c>
       <c r="I67" s="4">
         <v>38</v>
       </c>
@@ -3221,8 +3481,12 @@
       <c r="F68" s="4">
         <v>8</v>
       </c>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
+      <c r="G68" s="4">
+        <v>38</v>
+      </c>
+      <c r="H68" s="4">
+        <v>10</v>
+      </c>
       <c r="I68" s="4">
         <v>38</v>
       </c>
@@ -3257,8 +3521,12 @@
       <c r="F69" s="4">
         <v>6</v>
       </c>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
+      <c r="G69" s="4">
+        <v>38</v>
+      </c>
+      <c r="H69" s="4">
+        <v>10</v>
+      </c>
       <c r="I69" s="4">
         <v>36</v>
       </c>
@@ -3293,8 +3561,12 @@
       <c r="F70" s="4">
         <v>4</v>
       </c>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
+      <c r="G70" s="4">
+        <v>39</v>
+      </c>
+      <c r="H70" s="4">
+        <v>10</v>
+      </c>
       <c r="I70" s="4">
         <v>39</v>
       </c>
@@ -3329,8 +3601,12 @@
       <c r="F71" s="4">
         <v>7</v>
       </c>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
+      <c r="G71" s="4">
+        <v>38</v>
+      </c>
+      <c r="H71" s="4">
+        <v>9</v>
+      </c>
       <c r="I71" s="4">
         <v>37</v>
       </c>
@@ -3365,8 +3641,12 @@
       <c r="F72" s="4">
         <v>6</v>
       </c>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
+      <c r="G72" s="4">
+        <v>38</v>
+      </c>
+      <c r="H72" s="4">
+        <v>8</v>
+      </c>
       <c r="I72" s="4">
         <v>28</v>
       </c>
@@ -3401,8 +3681,12 @@
       <c r="F73" s="4">
         <v>7</v>
       </c>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
+      <c r="G73" s="4">
+        <v>32</v>
+      </c>
+      <c r="H73" s="4">
+        <v>10</v>
+      </c>
       <c r="I73" s="4">
         <v>31</v>
       </c>
@@ -3437,8 +3721,12 @@
       <c r="F74" s="4">
         <v>0</v>
       </c>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
+      <c r="G74" s="4">
+        <v>29</v>
+      </c>
+      <c r="H74" s="4">
+        <v>9</v>
+      </c>
       <c r="I74" s="4">
         <v>27</v>
       </c>
@@ -3473,8 +3761,12 @@
       <c r="F75" s="4">
         <v>8</v>
       </c>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
+      <c r="G75" s="4">
+        <v>39</v>
+      </c>
+      <c r="H75" s="4">
+        <v>10</v>
+      </c>
       <c r="I75" s="4">
         <v>35</v>
       </c>
@@ -3509,8 +3801,12 @@
       <c r="F76" s="4">
         <v>5</v>
       </c>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
+      <c r="G76" s="4">
+        <v>34</v>
+      </c>
+      <c r="H76" s="4">
+        <v>9</v>
+      </c>
       <c r="I76" s="4">
         <v>35</v>
       </c>
@@ -3545,8 +3841,12 @@
       <c r="F77" s="4">
         <v>5</v>
       </c>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
+      <c r="G77" s="4">
+        <v>37</v>
+      </c>
+      <c r="H77" s="4">
+        <v>8</v>
+      </c>
       <c r="I77" s="4">
         <v>34</v>
       </c>
@@ -3581,8 +3881,12 @@
       <c r="F78" s="4">
         <v>6</v>
       </c>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
+      <c r="G78" s="4">
+        <v>36</v>
+      </c>
+      <c r="H78" s="4">
+        <v>8</v>
+      </c>
       <c r="I78" s="4">
         <v>30</v>
       </c>
@@ -3617,8 +3921,12 @@
       <c r="F79" s="4">
         <v>6</v>
       </c>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
+      <c r="G79" s="4">
+        <v>38</v>
+      </c>
+      <c r="H79" s="4">
+        <v>8</v>
+      </c>
       <c r="I79" s="4">
         <v>32</v>
       </c>
@@ -3653,8 +3961,12 @@
       <c r="F80" s="4">
         <v>6</v>
       </c>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
+      <c r="G80" s="4">
+        <v>27</v>
+      </c>
+      <c r="H80" s="4">
+        <v>9</v>
+      </c>
       <c r="I80" s="4">
         <v>31</v>
       </c>
@@ -3689,8 +4001,12 @@
       <c r="F81" s="4">
         <v>6</v>
       </c>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
+      <c r="G81" s="4">
+        <v>29</v>
+      </c>
+      <c r="H81" s="4">
+        <v>7</v>
+      </c>
       <c r="I81" s="4">
         <v>35</v>
       </c>
@@ -3725,8 +4041,12 @@
       <c r="F82" s="4">
         <v>7</v>
       </c>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
+      <c r="G82" s="4">
+        <v>33</v>
+      </c>
+      <c r="H82" s="4">
+        <v>9</v>
+      </c>
       <c r="I82" s="4">
         <v>29</v>
       </c>
@@ -3761,8 +4081,12 @@
       <c r="F83" s="4">
         <v>6</v>
       </c>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
+      <c r="G83" s="4">
+        <v>39</v>
+      </c>
+      <c r="H83" s="4">
+        <v>7</v>
+      </c>
       <c r="I83" s="4">
         <v>32</v>
       </c>
@@ -3797,8 +4121,12 @@
       <c r="F84" s="4">
         <v>0</v>
       </c>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4"/>
+      <c r="G84" s="4">
+        <v>35</v>
+      </c>
+      <c r="H84" s="4">
+        <v>7</v>
+      </c>
       <c r="I84" s="4">
         <v>23</v>
       </c>
@@ -3833,8 +4161,12 @@
       <c r="F85" s="4">
         <v>8</v>
       </c>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
+      <c r="G85" s="4">
+        <v>38</v>
+      </c>
+      <c r="H85" s="4">
+        <v>10</v>
+      </c>
       <c r="I85" s="4">
         <v>40</v>
       </c>
@@ -3869,8 +4201,12 @@
       <c r="F86" s="4">
         <v>9</v>
       </c>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
+      <c r="G86" s="4">
+        <v>40</v>
+      </c>
+      <c r="H86" s="4">
+        <v>10</v>
+      </c>
       <c r="I86" s="4">
         <v>32</v>
       </c>
@@ -3905,8 +4241,12 @@
       <c r="F87" s="4">
         <v>6</v>
       </c>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
+      <c r="G87" s="4">
+        <v>36</v>
+      </c>
+      <c r="H87" s="4">
+        <v>9</v>
+      </c>
       <c r="I87" s="4">
         <v>31</v>
       </c>
@@ -3941,8 +4281,12 @@
       <c r="F88" s="4">
         <v>0</v>
       </c>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
+      <c r="G88" s="4">
+        <v>28</v>
+      </c>
+      <c r="H88" s="4">
+        <v>4</v>
+      </c>
       <c r="I88" s="4">
         <v>18</v>
       </c>
@@ -3977,8 +4321,12 @@
       <c r="F89" s="4">
         <v>7</v>
       </c>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
+      <c r="G89" s="4">
+        <v>32</v>
+      </c>
+      <c r="H89" s="4">
+        <v>8</v>
+      </c>
       <c r="I89" s="4">
         <v>38</v>
       </c>
@@ -4013,8 +4361,12 @@
       <c r="F90" s="4">
         <v>7</v>
       </c>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
+      <c r="G90" s="4">
+        <v>39</v>
+      </c>
+      <c r="H90" s="4">
+        <v>10</v>
+      </c>
       <c r="I90" s="4">
         <v>32</v>
       </c>
@@ -4049,8 +4401,12 @@
       <c r="F91" s="4">
         <v>8</v>
       </c>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
+      <c r="G91" s="4">
+        <v>38</v>
+      </c>
+      <c r="H91" s="4">
+        <v>8</v>
+      </c>
       <c r="I91" s="4">
         <v>36</v>
       </c>
@@ -4085,8 +4441,12 @@
       <c r="F92" s="4">
         <v>4</v>
       </c>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
+      <c r="G92" s="4">
+        <v>38</v>
+      </c>
+      <c r="H92" s="4">
+        <v>8</v>
+      </c>
       <c r="I92" s="4">
         <v>34</v>
       </c>
@@ -4121,8 +4481,12 @@
       <c r="F93" s="4">
         <v>5</v>
       </c>
-      <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
+      <c r="G93" s="4">
+        <v>34</v>
+      </c>
+      <c r="H93" s="4">
+        <v>8</v>
+      </c>
       <c r="I93" s="4">
         <v>25</v>
       </c>
@@ -4157,8 +4521,12 @@
       <c r="F94" s="4">
         <v>6</v>
       </c>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
+      <c r="G94" s="4">
+        <v>37</v>
+      </c>
+      <c r="H94" s="4">
+        <v>9</v>
+      </c>
       <c r="I94" s="4">
         <v>36</v>
       </c>
@@ -4193,8 +4561,12 @@
       <c r="F95" s="4">
         <v>6</v>
       </c>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
+      <c r="G95" s="4">
+        <v>31</v>
+      </c>
+      <c r="H95" s="4">
+        <v>7</v>
+      </c>
       <c r="I95" s="4">
         <v>35</v>
       </c>
@@ -4229,8 +4601,12 @@
       <c r="F96" s="4">
         <v>7</v>
       </c>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
+      <c r="G96" s="4">
+        <v>34</v>
+      </c>
+      <c r="H96" s="4">
+        <v>9</v>
+      </c>
       <c r="I96" s="4">
         <v>29</v>
       </c>
@@ -4265,8 +4641,12 @@
       <c r="F97" s="4">
         <v>9</v>
       </c>
-      <c r="G97" s="4"/>
-      <c r="H97" s="4"/>
+      <c r="G97" s="4">
+        <v>39</v>
+      </c>
+      <c r="H97" s="4">
+        <v>10</v>
+      </c>
       <c r="I97" s="4">
         <v>36</v>
       </c>
@@ -4301,8 +4681,12 @@
       <c r="F98" s="4">
         <v>8</v>
       </c>
-      <c r="G98" s="4"/>
-      <c r="H98" s="4"/>
+      <c r="G98" s="4">
+        <v>34</v>
+      </c>
+      <c r="H98" s="4">
+        <v>10</v>
+      </c>
       <c r="I98" s="4">
         <v>35</v>
       </c>
@@ -4337,8 +4721,12 @@
       <c r="F99" s="4">
         <v>4</v>
       </c>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
+      <c r="G99" s="4">
+        <v>39</v>
+      </c>
+      <c r="H99" s="4">
+        <v>10</v>
+      </c>
       <c r="I99" s="4">
         <v>32</v>
       </c>
@@ -4373,8 +4761,12 @@
       <c r="F100" s="4">
         <v>9</v>
       </c>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4"/>
+      <c r="G100" s="4">
+        <v>40</v>
+      </c>
+      <c r="H100" s="4">
+        <v>10</v>
+      </c>
       <c r="I100" s="4">
         <v>36</v>
       </c>
@@ -4409,8 +4801,12 @@
       <c r="F101" s="4">
         <v>9</v>
       </c>
-      <c r="G101" s="4"/>
-      <c r="H101" s="4"/>
+      <c r="G101" s="4">
+        <v>40</v>
+      </c>
+      <c r="H101" s="4">
+        <v>10</v>
+      </c>
       <c r="I101" s="4">
         <v>36</v>
       </c>
@@ -4445,8 +4841,12 @@
       <c r="F102" s="4">
         <v>7</v>
       </c>
-      <c r="G102" s="4"/>
-      <c r="H102" s="4"/>
+      <c r="G102" s="4">
+        <v>36</v>
+      </c>
+      <c r="H102" s="4">
+        <v>8</v>
+      </c>
       <c r="I102" s="4">
         <v>31</v>
       </c>
@@ -4481,8 +4881,12 @@
       <c r="F103" s="4">
         <v>9</v>
       </c>
-      <c r="G103" s="4"/>
-      <c r="H103" s="4"/>
+      <c r="G103" s="4">
+        <v>39</v>
+      </c>
+      <c r="H103" s="4">
+        <v>10</v>
+      </c>
       <c r="I103" s="4">
         <v>37</v>
       </c>
@@ -4517,8 +4921,12 @@
       <c r="F104" s="4">
         <v>8</v>
       </c>
-      <c r="G104" s="4"/>
-      <c r="H104" s="4"/>
+      <c r="G104" s="4">
+        <v>35</v>
+      </c>
+      <c r="H104" s="4">
+        <v>8</v>
+      </c>
       <c r="I104" s="4">
         <v>36</v>
       </c>

--- a/m3.xlsx
+++ b/m3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\سعيات\م2 - ف2\steam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B386E296-F48E-4726-8983-6699C850318A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C568C73-0BCC-4C00-A48E-B864A48B5455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -318,9 +318,6 @@
     <t>منتظر حيدر خليل ابراهيم</t>
   </si>
   <si>
-    <t>منتظر يوسف حميد شويلي</t>
-  </si>
-  <si>
     <t>مهدي احمد عبد الامير عبد الحسين</t>
   </si>
   <si>
@@ -370,6 +367,9 @@
   </si>
   <si>
     <t>رقيه محسن جبير ناصر</t>
+  </si>
+  <si>
+    <t>منتظر يوسف حميد كاظم</t>
   </si>
 </sst>
 </file>
@@ -765,6 +765,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E830AE-5C32-4A25-A5BE-EAB4941C3B09}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:P123"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -798,23 +801,23 @@
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F1" s="8"/>
       <c r="G1" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J1" s="8"/>
       <c r="K1" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L1" s="8"/>
       <c r="M1" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N1" s="8"/>
       <c r="O1" s="7"/>
@@ -893,8 +896,12 @@
       <c r="J3" s="4">
         <v>10</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
+      <c r="K3" s="4">
+        <v>29</v>
+      </c>
+      <c r="L3" s="4">
+        <v>6</v>
+      </c>
       <c r="M3" s="4">
         <v>24</v>
       </c>
@@ -933,8 +940,12 @@
       <c r="J4" s="4">
         <v>10</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
+      <c r="K4" s="4">
+        <v>29</v>
+      </c>
+      <c r="L4" s="4">
+        <v>5</v>
+      </c>
       <c r="M4" s="4">
         <v>23</v>
       </c>
@@ -973,8 +984,12 @@
       <c r="J5" s="4">
         <v>10</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
+      <c r="K5" s="4">
+        <v>28</v>
+      </c>
+      <c r="L5" s="4">
+        <v>6</v>
+      </c>
       <c r="M5" s="4">
         <v>9</v>
       </c>
@@ -1013,8 +1028,12 @@
       <c r="J6" s="4">
         <v>9</v>
       </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
+      <c r="K6" s="4">
+        <v>33</v>
+      </c>
+      <c r="L6" s="4">
+        <v>10</v>
+      </c>
       <c r="M6" s="4">
         <v>24</v>
       </c>
@@ -1053,8 +1072,12 @@
       <c r="J7" s="4">
         <v>7</v>
       </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
+      <c r="K7" s="4">
+        <v>35</v>
+      </c>
+      <c r="L7" s="4">
+        <v>10</v>
+      </c>
       <c r="M7" s="4">
         <v>26</v>
       </c>
@@ -1093,8 +1116,12 @@
       <c r="J8" s="4">
         <v>10</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
+      <c r="K8" s="4">
+        <v>40</v>
+      </c>
+      <c r="L8" s="4">
+        <v>10</v>
+      </c>
       <c r="M8" s="4">
         <v>40</v>
       </c>
@@ -1133,8 +1160,12 @@
       <c r="J9" s="4">
         <v>9</v>
       </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
+      <c r="K9" s="4">
+        <v>32</v>
+      </c>
+      <c r="L9" s="4">
+        <v>5</v>
+      </c>
       <c r="M9" s="4">
         <v>28</v>
       </c>
@@ -1173,8 +1204,12 @@
       <c r="J10" s="4">
         <v>10</v>
       </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
+      <c r="K10" s="4">
+        <v>30</v>
+      </c>
+      <c r="L10" s="4">
+        <v>7</v>
+      </c>
       <c r="M10" s="4">
         <v>25</v>
       </c>
@@ -1213,8 +1248,12 @@
       <c r="J11" s="4">
         <v>10</v>
       </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
+      <c r="K11" s="4">
+        <v>33</v>
+      </c>
+      <c r="L11" s="4">
+        <v>9</v>
+      </c>
       <c r="M11" s="4">
         <v>27</v>
       </c>
@@ -1253,8 +1292,12 @@
       <c r="J12" s="4">
         <v>10</v>
       </c>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
+      <c r="K12" s="4">
+        <v>40</v>
+      </c>
+      <c r="L12" s="4">
+        <v>10</v>
+      </c>
       <c r="M12" s="4">
         <v>40</v>
       </c>
@@ -1293,8 +1336,12 @@
       <c r="J13" s="4">
         <v>10</v>
       </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
+      <c r="K13" s="4">
+        <v>40</v>
+      </c>
+      <c r="L13" s="4">
+        <v>10</v>
+      </c>
       <c r="M13" s="4">
         <v>40</v>
       </c>
@@ -1333,8 +1380,12 @@
       <c r="J14" s="4">
         <v>10</v>
       </c>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
+      <c r="K14" s="4">
+        <v>37</v>
+      </c>
+      <c r="L14" s="4">
+        <v>10</v>
+      </c>
       <c r="M14" s="4">
         <v>32</v>
       </c>
@@ -1373,8 +1424,12 @@
       <c r="J15" s="4">
         <v>10</v>
       </c>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
+      <c r="K15" s="4">
+        <v>28</v>
+      </c>
+      <c r="L15" s="4">
+        <v>5</v>
+      </c>
       <c r="M15" s="4">
         <v>21</v>
       </c>
@@ -1413,8 +1468,12 @@
       <c r="J16" s="4">
         <v>9</v>
       </c>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
+      <c r="K16" s="4">
+        <v>35</v>
+      </c>
+      <c r="L16" s="4">
+        <v>10</v>
+      </c>
       <c r="M16" s="4">
         <v>25</v>
       </c>
@@ -1453,8 +1512,12 @@
       <c r="J17" s="4">
         <v>10</v>
       </c>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
+      <c r="K17" s="4">
+        <v>36</v>
+      </c>
+      <c r="L17" s="4">
+        <v>10</v>
+      </c>
       <c r="M17" s="4">
         <v>30</v>
       </c>
@@ -1493,8 +1556,12 @@
       <c r="J18" s="4">
         <v>2</v>
       </c>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
+      <c r="K18" s="4">
+        <v>33</v>
+      </c>
+      <c r="L18" s="4">
+        <v>5</v>
+      </c>
       <c r="M18" s="4">
         <v>26</v>
       </c>
@@ -1533,8 +1600,12 @@
       <c r="J19" s="4">
         <v>8</v>
       </c>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
+      <c r="K19" s="4">
+        <v>31</v>
+      </c>
+      <c r="L19" s="4">
+        <v>9</v>
+      </c>
       <c r="M19" s="4">
         <v>29</v>
       </c>
@@ -1573,8 +1644,12 @@
       <c r="J20" s="4">
         <v>9</v>
       </c>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
+      <c r="K20" s="4">
+        <v>33</v>
+      </c>
+      <c r="L20" s="4">
+        <v>9</v>
+      </c>
       <c r="M20" s="4">
         <v>32</v>
       </c>
@@ -1613,8 +1688,12 @@
       <c r="J21" s="4">
         <v>9</v>
       </c>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
+      <c r="K21" s="4">
+        <v>30</v>
+      </c>
+      <c r="L21" s="4">
+        <v>7</v>
+      </c>
       <c r="M21" s="4">
         <v>25</v>
       </c>
@@ -1653,8 +1732,12 @@
       <c r="J22" s="4">
         <v>8</v>
       </c>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
+      <c r="K22" s="4">
+        <v>30</v>
+      </c>
+      <c r="L22" s="4">
+        <v>6</v>
+      </c>
       <c r="M22" s="4">
         <v>25</v>
       </c>
@@ -1693,8 +1776,12 @@
       <c r="J23" s="4">
         <v>8</v>
       </c>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
+      <c r="K23" s="4">
+        <v>26</v>
+      </c>
+      <c r="L23" s="4">
+        <v>4</v>
+      </c>
       <c r="M23" s="4">
         <v>28</v>
       </c>
@@ -1733,8 +1820,12 @@
       <c r="J24" s="4">
         <v>10</v>
       </c>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
+      <c r="K24" s="4">
+        <v>30</v>
+      </c>
+      <c r="L24" s="4">
+        <v>4</v>
+      </c>
       <c r="M24" s="4">
         <v>26</v>
       </c>
@@ -1773,8 +1864,12 @@
       <c r="J25" s="4">
         <v>7</v>
       </c>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
+      <c r="K25" s="4">
+        <v>32</v>
+      </c>
+      <c r="L25" s="4">
+        <v>6</v>
+      </c>
       <c r="M25" s="4">
         <v>25</v>
       </c>
@@ -1813,8 +1908,12 @@
       <c r="J26" s="4">
         <v>9</v>
       </c>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
+      <c r="K26" s="4">
+        <v>40</v>
+      </c>
+      <c r="L26" s="4">
+        <v>9</v>
+      </c>
       <c r="M26" s="4">
         <v>40</v>
       </c>
@@ -1853,8 +1952,12 @@
       <c r="J27" s="4">
         <v>6</v>
       </c>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
+      <c r="K27" s="4">
+        <v>28</v>
+      </c>
+      <c r="L27" s="4">
+        <v>6</v>
+      </c>
       <c r="M27" s="4">
         <v>24</v>
       </c>
@@ -1893,8 +1996,12 @@
       <c r="J28" s="4">
         <v>9</v>
       </c>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
+      <c r="K28" s="4">
+        <v>32</v>
+      </c>
+      <c r="L28" s="4">
+        <v>6</v>
+      </c>
       <c r="M28" s="4">
         <v>27</v>
       </c>
@@ -1933,8 +2040,12 @@
       <c r="J29" s="4">
         <v>10</v>
       </c>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
+      <c r="K29" s="4">
+        <v>32</v>
+      </c>
+      <c r="L29" s="4">
+        <v>8</v>
+      </c>
       <c r="M29" s="4">
         <v>26</v>
       </c>
@@ -1973,8 +2084,12 @@
       <c r="J30" s="4">
         <v>8</v>
       </c>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
+      <c r="K30" s="4">
+        <v>32</v>
+      </c>
+      <c r="L30" s="4">
+        <v>10</v>
+      </c>
       <c r="M30" s="4">
         <v>25</v>
       </c>
@@ -2013,8 +2128,12 @@
       <c r="J31" s="4">
         <v>10</v>
       </c>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
+      <c r="K31" s="4">
+        <v>37</v>
+      </c>
+      <c r="L31" s="4">
+        <v>10</v>
+      </c>
       <c r="M31" s="4">
         <v>32</v>
       </c>
@@ -2053,8 +2172,12 @@
       <c r="J32" s="4">
         <v>10</v>
       </c>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
+      <c r="K32" s="4">
+        <v>36</v>
+      </c>
+      <c r="L32" s="4">
+        <v>10</v>
+      </c>
       <c r="M32" s="4">
         <v>35</v>
       </c>
@@ -2093,8 +2216,12 @@
       <c r="J33" s="4">
         <v>8</v>
       </c>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
+      <c r="K33" s="4">
+        <v>37</v>
+      </c>
+      <c r="L33" s="4">
+        <v>10</v>
+      </c>
       <c r="M33" s="4">
         <v>37</v>
       </c>
@@ -2133,8 +2260,12 @@
       <c r="J34" s="4">
         <v>10</v>
       </c>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
+      <c r="K34" s="4">
+        <v>35</v>
+      </c>
+      <c r="L34" s="4">
+        <v>10</v>
+      </c>
       <c r="M34" s="4">
         <v>29</v>
       </c>
@@ -2147,7 +2278,7 @@
         <v>3033</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C35" s="3">
         <v>38</v>
@@ -2173,8 +2304,12 @@
       <c r="J35" s="4">
         <v>10</v>
       </c>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
+      <c r="K35" s="4">
+        <v>36</v>
+      </c>
+      <c r="L35" s="4">
+        <v>10</v>
+      </c>
       <c r="M35" s="4">
         <v>36</v>
       </c>
@@ -2213,8 +2348,12 @@
       <c r="J36" s="4">
         <v>10</v>
       </c>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
+      <c r="K36" s="4">
+        <v>39</v>
+      </c>
+      <c r="L36" s="4">
+        <v>10</v>
+      </c>
       <c r="M36" s="4">
         <v>27</v>
       </c>
@@ -2253,8 +2392,12 @@
       <c r="J37" s="4">
         <v>10</v>
       </c>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
+      <c r="K37" s="4">
+        <v>40</v>
+      </c>
+      <c r="L37" s="4">
+        <v>10</v>
+      </c>
       <c r="M37" s="4">
         <v>40</v>
       </c>
@@ -2293,8 +2436,12 @@
       <c r="J38" s="4">
         <v>10</v>
       </c>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
+      <c r="K38" s="4">
+        <v>30</v>
+      </c>
+      <c r="L38" s="4">
+        <v>10</v>
+      </c>
       <c r="M38" s="4">
         <v>32</v>
       </c>
@@ -2333,8 +2480,12 @@
       <c r="J39" s="4">
         <v>10</v>
       </c>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
+      <c r="K39" s="4">
+        <v>33</v>
+      </c>
+      <c r="L39" s="4">
+        <v>5</v>
+      </c>
       <c r="M39" s="4">
         <v>27</v>
       </c>
@@ -2373,8 +2524,12 @@
       <c r="J40" s="4">
         <v>7</v>
       </c>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
+      <c r="K40" s="4">
+        <v>34</v>
+      </c>
+      <c r="L40" s="4">
+        <v>10</v>
+      </c>
       <c r="M40" s="4">
         <v>32</v>
       </c>
@@ -2413,8 +2568,12 @@
       <c r="J41" s="4">
         <v>10</v>
       </c>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
+      <c r="K41" s="4">
+        <v>38</v>
+      </c>
+      <c r="L41" s="4">
+        <v>10</v>
+      </c>
       <c r="M41" s="4">
         <v>32</v>
       </c>
@@ -2453,8 +2612,12 @@
       <c r="J42" s="4">
         <v>9</v>
       </c>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
+      <c r="K42" s="4">
+        <v>33</v>
+      </c>
+      <c r="L42" s="4">
+        <v>8</v>
+      </c>
       <c r="M42" s="4">
         <v>19</v>
       </c>
@@ -2493,8 +2656,12 @@
       <c r="J43" s="4">
         <v>7</v>
       </c>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
+      <c r="K43" s="4">
+        <v>32</v>
+      </c>
+      <c r="L43" s="4">
+        <v>7</v>
+      </c>
       <c r="M43" s="4">
         <v>22</v>
       </c>
@@ -2533,8 +2700,12 @@
       <c r="J44" s="4">
         <v>10</v>
       </c>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
+      <c r="K44" s="4">
+        <v>40</v>
+      </c>
+      <c r="L44" s="4">
+        <v>10</v>
+      </c>
       <c r="M44" s="4">
         <v>40</v>
       </c>
@@ -2573,8 +2744,12 @@
       <c r="J45" s="4">
         <v>9</v>
       </c>
-      <c r="K45" s="4"/>
-      <c r="L45" s="4"/>
+      <c r="K45" s="4">
+        <v>35</v>
+      </c>
+      <c r="L45" s="4">
+        <v>4</v>
+      </c>
       <c r="M45" s="4">
         <v>25</v>
       </c>
@@ -2613,8 +2788,12 @@
       <c r="J46" s="4">
         <v>10</v>
       </c>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
+      <c r="K46" s="4">
+        <v>37</v>
+      </c>
+      <c r="L46" s="4">
+        <v>9</v>
+      </c>
       <c r="M46" s="4">
         <v>30</v>
       </c>
@@ -2653,8 +2832,12 @@
       <c r="J47" s="4">
         <v>8</v>
       </c>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
+      <c r="K47" s="4">
+        <v>34</v>
+      </c>
+      <c r="L47" s="4">
+        <v>8</v>
+      </c>
       <c r="M47" s="4">
         <v>26</v>
       </c>
@@ -2693,8 +2876,12 @@
       <c r="J48" s="4">
         <v>8</v>
       </c>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
+      <c r="K48" s="4">
+        <v>26</v>
+      </c>
+      <c r="L48" s="4">
+        <v>5</v>
+      </c>
       <c r="M48" s="4">
         <v>23</v>
       </c>
@@ -2733,8 +2920,12 @@
       <c r="J49" s="4">
         <v>9</v>
       </c>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
+      <c r="K49" s="4">
+        <v>31</v>
+      </c>
+      <c r="L49" s="4">
+        <v>10</v>
+      </c>
       <c r="M49" s="4">
         <v>27</v>
       </c>
@@ -2773,8 +2964,12 @@
       <c r="J50" s="4">
         <v>10</v>
       </c>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
+      <c r="K50" s="4">
+        <v>33</v>
+      </c>
+      <c r="L50" s="4">
+        <v>5</v>
+      </c>
       <c r="M50" s="4">
         <v>26</v>
       </c>
@@ -2813,8 +3008,12 @@
       <c r="J51" s="4">
         <v>9</v>
       </c>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
+      <c r="K51" s="4">
+        <v>30</v>
+      </c>
+      <c r="L51" s="4">
+        <v>8</v>
+      </c>
       <c r="M51" s="4">
         <v>24</v>
       </c>
@@ -2853,8 +3052,12 @@
       <c r="J52" s="4">
         <v>9</v>
       </c>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
+      <c r="K52" s="4">
+        <v>37</v>
+      </c>
+      <c r="L52" s="4">
+        <v>7</v>
+      </c>
       <c r="M52" s="4">
         <v>34</v>
       </c>
@@ -2893,8 +3096,12 @@
       <c r="J53" s="4">
         <v>9</v>
       </c>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
+      <c r="K53" s="4">
+        <v>32</v>
+      </c>
+      <c r="L53" s="4">
+        <v>5</v>
+      </c>
       <c r="M53" s="4">
         <v>30</v>
       </c>
@@ -2933,8 +3140,12 @@
       <c r="J54" s="4">
         <v>9</v>
       </c>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
+      <c r="K54" s="4">
+        <v>34</v>
+      </c>
+      <c r="L54" s="4">
+        <v>4</v>
+      </c>
       <c r="M54" s="4">
         <v>26</v>
       </c>
@@ -2973,8 +3184,12 @@
       <c r="J55" s="4">
         <v>8</v>
       </c>
-      <c r="K55" s="4"/>
-      <c r="L55" s="4"/>
+      <c r="K55" s="4">
+        <v>33</v>
+      </c>
+      <c r="L55" s="4">
+        <v>8</v>
+      </c>
       <c r="M55" s="4">
         <v>26</v>
       </c>
@@ -3013,8 +3228,12 @@
       <c r="J56" s="4">
         <v>8</v>
       </c>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
+      <c r="K56" s="4">
+        <v>33</v>
+      </c>
+      <c r="L56" s="4">
+        <v>6</v>
+      </c>
       <c r="M56" s="4">
         <v>27</v>
       </c>
@@ -3053,8 +3272,12 @@
       <c r="J57" s="4">
         <v>10</v>
       </c>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
+      <c r="K57" s="4">
+        <v>40</v>
+      </c>
+      <c r="L57" s="4">
+        <v>10</v>
+      </c>
       <c r="M57" s="4">
         <v>40</v>
       </c>
@@ -3093,8 +3316,12 @@
       <c r="J58" s="4">
         <v>8</v>
       </c>
-      <c r="K58" s="4"/>
-      <c r="L58" s="4"/>
+      <c r="K58" s="4">
+        <v>33</v>
+      </c>
+      <c r="L58" s="4">
+        <v>4</v>
+      </c>
       <c r="M58" s="4">
         <v>29</v>
       </c>
@@ -3133,8 +3360,12 @@
       <c r="J59" s="4">
         <v>10</v>
       </c>
-      <c r="K59" s="4"/>
-      <c r="L59" s="4"/>
+      <c r="K59" s="4">
+        <v>40</v>
+      </c>
+      <c r="L59" s="4">
+        <v>10</v>
+      </c>
       <c r="M59" s="4">
         <v>36</v>
       </c>
@@ -3173,8 +3404,12 @@
       <c r="J60" s="4">
         <v>10</v>
       </c>
-      <c r="K60" s="4"/>
-      <c r="L60" s="4"/>
+      <c r="K60" s="4">
+        <v>38</v>
+      </c>
+      <c r="L60" s="4">
+        <v>10</v>
+      </c>
       <c r="M60" s="4">
         <v>30</v>
       </c>
@@ -3213,8 +3448,12 @@
       <c r="J61" s="4">
         <v>10</v>
       </c>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4"/>
+      <c r="K61" s="4">
+        <v>36</v>
+      </c>
+      <c r="L61" s="4">
+        <v>9</v>
+      </c>
       <c r="M61" s="4">
         <v>26</v>
       </c>
@@ -3253,8 +3492,12 @@
       <c r="J62" s="4">
         <v>9</v>
       </c>
-      <c r="K62" s="4"/>
-      <c r="L62" s="4"/>
+      <c r="K62" s="4">
+        <v>35</v>
+      </c>
+      <c r="L62" s="4">
+        <v>5</v>
+      </c>
       <c r="M62" s="4">
         <v>25</v>
       </c>
@@ -3293,8 +3536,12 @@
       <c r="J63" s="4">
         <v>10</v>
       </c>
-      <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
+      <c r="K63" s="4">
+        <v>34</v>
+      </c>
+      <c r="L63" s="4">
+        <v>7</v>
+      </c>
       <c r="M63" s="4">
         <v>25</v>
       </c>
@@ -3333,8 +3580,12 @@
       <c r="J64" s="4">
         <v>10</v>
       </c>
-      <c r="K64" s="4"/>
-      <c r="L64" s="4"/>
+      <c r="K64" s="4">
+        <v>35</v>
+      </c>
+      <c r="L64" s="4">
+        <v>7</v>
+      </c>
       <c r="M64" s="4">
         <v>28</v>
       </c>
@@ -3373,8 +3624,12 @@
       <c r="J65" s="4">
         <v>8</v>
       </c>
-      <c r="K65" s="4"/>
-      <c r="L65" s="4"/>
+      <c r="K65" s="4">
+        <v>35</v>
+      </c>
+      <c r="L65" s="4">
+        <v>6</v>
+      </c>
       <c r="M65" s="4">
         <v>27</v>
       </c>
@@ -3413,8 +3668,12 @@
       <c r="J66" s="4">
         <v>9</v>
       </c>
-      <c r="K66" s="4"/>
-      <c r="L66" s="4"/>
+      <c r="K66" s="4">
+        <v>35</v>
+      </c>
+      <c r="L66" s="4">
+        <v>5</v>
+      </c>
       <c r="M66" s="4">
         <v>23</v>
       </c>
@@ -3453,8 +3712,12 @@
       <c r="J67" s="4">
         <v>10</v>
       </c>
-      <c r="K67" s="4"/>
-      <c r="L67" s="4"/>
+      <c r="K67" s="4">
+        <v>37</v>
+      </c>
+      <c r="L67" s="4">
+        <v>9</v>
+      </c>
       <c r="M67" s="4">
         <v>32</v>
       </c>
@@ -3493,8 +3756,12 @@
       <c r="J68" s="4">
         <v>10</v>
       </c>
-      <c r="K68" s="4"/>
-      <c r="L68" s="4"/>
+      <c r="K68" s="4">
+        <v>37</v>
+      </c>
+      <c r="L68" s="4">
+        <v>10</v>
+      </c>
       <c r="M68" s="4">
         <v>36</v>
       </c>
@@ -3533,8 +3800,12 @@
       <c r="J69" s="4">
         <v>10</v>
       </c>
-      <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
+      <c r="K69" s="4">
+        <v>38</v>
+      </c>
+      <c r="L69" s="4">
+        <v>10</v>
+      </c>
       <c r="M69" s="4">
         <v>33</v>
       </c>
@@ -3573,8 +3844,12 @@
       <c r="J70" s="4">
         <v>10</v>
       </c>
-      <c r="K70" s="4"/>
-      <c r="L70" s="4"/>
+      <c r="K70" s="4">
+        <v>38</v>
+      </c>
+      <c r="L70" s="4">
+        <v>10</v>
+      </c>
       <c r="M70" s="4">
         <v>37</v>
       </c>
@@ -3613,8 +3888,12 @@
       <c r="J71" s="4">
         <v>9</v>
       </c>
-      <c r="K71" s="4"/>
-      <c r="L71" s="4"/>
+      <c r="K71" s="4">
+        <v>34</v>
+      </c>
+      <c r="L71" s="4">
+        <v>6</v>
+      </c>
       <c r="M71" s="4">
         <v>25</v>
       </c>
@@ -3653,8 +3932,12 @@
       <c r="J72" s="4">
         <v>10</v>
       </c>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
+      <c r="K72" s="4">
+        <v>34</v>
+      </c>
+      <c r="L72" s="4">
+        <v>7</v>
+      </c>
       <c r="M72" s="4">
         <v>29</v>
       </c>
@@ -3693,8 +3976,12 @@
       <c r="J73" s="4">
         <v>10</v>
       </c>
-      <c r="K73" s="4"/>
-      <c r="L73" s="4"/>
+      <c r="K73" s="4">
+        <v>33</v>
+      </c>
+      <c r="L73" s="4">
+        <v>10</v>
+      </c>
       <c r="M73" s="4">
         <v>24</v>
       </c>
@@ -3733,8 +4020,12 @@
       <c r="J74" s="4">
         <v>6</v>
       </c>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
+      <c r="K74" s="4">
+        <v>28</v>
+      </c>
+      <c r="L74" s="4">
+        <v>2</v>
+      </c>
       <c r="M74" s="4">
         <v>15</v>
       </c>
@@ -3773,8 +4064,12 @@
       <c r="J75" s="4">
         <v>10</v>
       </c>
-      <c r="K75" s="4"/>
-      <c r="L75" s="4"/>
+      <c r="K75" s="4">
+        <v>38</v>
+      </c>
+      <c r="L75" s="4">
+        <v>10</v>
+      </c>
       <c r="M75" s="4">
         <v>40</v>
       </c>
@@ -3813,8 +4108,12 @@
       <c r="J76" s="4">
         <v>10</v>
       </c>
-      <c r="K76" s="4"/>
-      <c r="L76" s="4"/>
+      <c r="K76" s="4">
+        <v>33</v>
+      </c>
+      <c r="L76" s="4">
+        <v>7</v>
+      </c>
       <c r="M76" s="4">
         <v>24</v>
       </c>
@@ -3853,8 +4152,12 @@
       <c r="J77" s="4">
         <v>10</v>
       </c>
-      <c r="K77" s="4"/>
-      <c r="L77" s="4"/>
+      <c r="K77" s="4">
+        <v>35</v>
+      </c>
+      <c r="L77" s="4">
+        <v>7</v>
+      </c>
       <c r="M77" s="4">
         <v>26</v>
       </c>
@@ -3893,8 +4196,12 @@
       <c r="J78" s="4">
         <v>10</v>
       </c>
-      <c r="K78" s="4"/>
-      <c r="L78" s="4"/>
+      <c r="K78" s="4">
+        <v>34</v>
+      </c>
+      <c r="L78" s="4">
+        <v>5</v>
+      </c>
       <c r="M78" s="4">
         <v>23</v>
       </c>
@@ -3933,8 +4240,12 @@
       <c r="J79" s="4">
         <v>8</v>
       </c>
-      <c r="K79" s="4"/>
-      <c r="L79" s="4"/>
+      <c r="K79" s="4">
+        <v>35</v>
+      </c>
+      <c r="L79" s="4">
+        <v>5</v>
+      </c>
       <c r="M79" s="4">
         <v>22</v>
       </c>
@@ -3973,8 +4284,12 @@
       <c r="J80" s="4">
         <v>7</v>
       </c>
-      <c r="K80" s="4"/>
-      <c r="L80" s="4"/>
+      <c r="K80" s="4">
+        <v>27</v>
+      </c>
+      <c r="L80" s="4">
+        <v>3</v>
+      </c>
       <c r="M80" s="4">
         <v>20</v>
       </c>
@@ -4013,8 +4328,12 @@
       <c r="J81" s="4">
         <v>9</v>
       </c>
-      <c r="K81" s="4"/>
-      <c r="L81" s="4"/>
+      <c r="K81" s="4">
+        <v>32</v>
+      </c>
+      <c r="L81" s="4">
+        <v>10</v>
+      </c>
       <c r="M81" s="4">
         <v>26</v>
       </c>
@@ -4053,8 +4372,12 @@
       <c r="J82" s="4">
         <v>9</v>
       </c>
-      <c r="K82" s="4"/>
-      <c r="L82" s="4"/>
+      <c r="K82" s="4">
+        <v>32</v>
+      </c>
+      <c r="L82" s="4">
+        <v>6</v>
+      </c>
       <c r="M82" s="4">
         <v>24</v>
       </c>
@@ -4093,8 +4416,12 @@
       <c r="J83" s="4">
         <v>6</v>
       </c>
-      <c r="K83" s="4"/>
-      <c r="L83" s="4"/>
+      <c r="K83" s="4">
+        <v>39</v>
+      </c>
+      <c r="L83" s="4">
+        <v>5</v>
+      </c>
       <c r="M83" s="4">
         <v>26</v>
       </c>
@@ -4133,8 +4460,12 @@
       <c r="J84" s="4">
         <v>7</v>
       </c>
-      <c r="K84" s="4"/>
-      <c r="L84" s="4"/>
+      <c r="K84" s="4">
+        <v>33</v>
+      </c>
+      <c r="L84" s="4">
+        <v>10</v>
+      </c>
       <c r="M84" s="4">
         <v>24</v>
       </c>
@@ -4173,8 +4504,12 @@
       <c r="J85" s="4">
         <v>10</v>
       </c>
-      <c r="K85" s="4"/>
-      <c r="L85" s="4"/>
+      <c r="K85" s="4">
+        <v>37</v>
+      </c>
+      <c r="L85" s="4">
+        <v>10</v>
+      </c>
       <c r="M85" s="4">
         <v>28</v>
       </c>
@@ -4213,8 +4548,12 @@
       <c r="J86" s="4">
         <v>8</v>
       </c>
-      <c r="K86" s="4"/>
-      <c r="L86" s="4"/>
+      <c r="K86" s="4">
+        <v>39</v>
+      </c>
+      <c r="L86" s="4">
+        <v>10</v>
+      </c>
       <c r="M86" s="4">
         <v>40</v>
       </c>
@@ -4253,8 +4592,12 @@
       <c r="J87" s="4">
         <v>9</v>
       </c>
-      <c r="K87" s="4"/>
-      <c r="L87" s="4"/>
+      <c r="K87" s="4">
+        <v>35</v>
+      </c>
+      <c r="L87" s="4">
+        <v>9</v>
+      </c>
       <c r="M87" s="4">
         <v>30</v>
       </c>
@@ -4293,8 +4636,12 @@
       <c r="J88" s="4">
         <v>7</v>
       </c>
-      <c r="K88" s="4"/>
-      <c r="L88" s="4"/>
+      <c r="K88" s="4">
+        <v>32</v>
+      </c>
+      <c r="L88" s="4">
+        <v>7</v>
+      </c>
       <c r="M88" s="4">
         <v>23</v>
       </c>
@@ -4333,8 +4680,12 @@
       <c r="J89" s="4">
         <v>10</v>
       </c>
-      <c r="K89" s="4"/>
-      <c r="L89" s="4"/>
+      <c r="K89" s="4">
+        <v>33</v>
+      </c>
+      <c r="L89" s="4">
+        <v>8</v>
+      </c>
       <c r="M89" s="4">
         <v>27</v>
       </c>
@@ -4373,8 +4724,12 @@
       <c r="J90" s="4">
         <v>9</v>
       </c>
-      <c r="K90" s="4"/>
-      <c r="L90" s="4"/>
+      <c r="K90" s="4">
+        <v>37</v>
+      </c>
+      <c r="L90" s="4">
+        <v>6</v>
+      </c>
       <c r="M90" s="4">
         <v>30</v>
       </c>
@@ -4413,8 +4768,12 @@
       <c r="J91" s="4">
         <v>10</v>
       </c>
-      <c r="K91" s="4"/>
-      <c r="L91" s="4"/>
+      <c r="K91" s="4">
+        <v>37</v>
+      </c>
+      <c r="L91" s="4">
+        <v>9</v>
+      </c>
       <c r="M91" s="4">
         <v>32</v>
       </c>
@@ -4453,8 +4812,12 @@
       <c r="J92" s="4">
         <v>8</v>
       </c>
-      <c r="K92" s="4"/>
-      <c r="L92" s="4"/>
+      <c r="K92" s="4">
+        <v>36</v>
+      </c>
+      <c r="L92" s="4">
+        <v>7</v>
+      </c>
       <c r="M92" s="4">
         <v>27</v>
       </c>
@@ -4467,7 +4830,7 @@
         <v>3091</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C93" s="3">
         <v>23</v>
@@ -4493,8 +4856,12 @@
       <c r="J93" s="4">
         <v>10</v>
       </c>
-      <c r="K93" s="4"/>
-      <c r="L93" s="4"/>
+      <c r="K93" s="4">
+        <v>35</v>
+      </c>
+      <c r="L93" s="4">
+        <v>6</v>
+      </c>
       <c r="M93" s="4">
         <v>22</v>
       </c>
@@ -4507,7 +4874,7 @@
         <v>3092</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C94" s="3">
         <v>14</v>
@@ -4533,8 +4900,12 @@
       <c r="J94" s="4">
         <v>9</v>
       </c>
-      <c r="K94" s="4"/>
-      <c r="L94" s="4"/>
+      <c r="K94" s="4">
+        <v>35</v>
+      </c>
+      <c r="L94" s="4">
+        <v>3</v>
+      </c>
       <c r="M94" s="4">
         <v>29</v>
       </c>
@@ -4547,7 +4918,7 @@
         <v>3093</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C95" s="3">
         <v>29</v>
@@ -4573,8 +4944,12 @@
       <c r="J95" s="4">
         <v>8</v>
       </c>
-      <c r="K95" s="4"/>
-      <c r="L95" s="4"/>
+      <c r="K95" s="4">
+        <v>31</v>
+      </c>
+      <c r="L95" s="4">
+        <v>9</v>
+      </c>
       <c r="M95" s="4">
         <v>27</v>
       </c>
@@ -4587,7 +4962,7 @@
         <v>3094</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C96" s="3">
         <v>32</v>
@@ -4613,8 +4988,12 @@
       <c r="J96" s="4">
         <v>8</v>
       </c>
-      <c r="K96" s="4"/>
-      <c r="L96" s="4"/>
+      <c r="K96" s="4">
+        <v>35</v>
+      </c>
+      <c r="L96" s="4">
+        <v>9</v>
+      </c>
       <c r="M96" s="4">
         <v>27</v>
       </c>
@@ -4627,7 +5006,7 @@
         <v>3095</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C97" s="3">
         <v>32</v>
@@ -4653,8 +5032,12 @@
       <c r="J97" s="4">
         <v>10</v>
       </c>
-      <c r="K97" s="4"/>
-      <c r="L97" s="4"/>
+      <c r="K97" s="4">
+        <v>35</v>
+      </c>
+      <c r="L97" s="4">
+        <v>10</v>
+      </c>
       <c r="M97" s="4">
         <v>30</v>
       </c>
@@ -4667,7 +5050,7 @@
         <v>3096</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C98" s="3">
         <v>29</v>
@@ -4693,8 +5076,12 @@
       <c r="J98" s="4">
         <v>10</v>
       </c>
-      <c r="K98" s="4"/>
-      <c r="L98" s="4"/>
+      <c r="K98" s="4">
+        <v>35</v>
+      </c>
+      <c r="L98" s="4">
+        <v>10</v>
+      </c>
       <c r="M98" s="4">
         <v>27</v>
       </c>
@@ -4707,7 +5094,7 @@
         <v>3097</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C99" s="3">
         <v>32</v>
@@ -4733,8 +5120,12 @@
       <c r="J99" s="4">
         <v>8</v>
       </c>
-      <c r="K99" s="4"/>
-      <c r="L99" s="4"/>
+      <c r="K99" s="4">
+        <v>37</v>
+      </c>
+      <c r="L99" s="4">
+        <v>10</v>
+      </c>
       <c r="M99" s="4">
         <v>31</v>
       </c>
@@ -4747,7 +5138,7 @@
         <v>3098</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C100" s="3">
         <v>29</v>
@@ -4773,8 +5164,12 @@
       <c r="J100" s="4">
         <v>8</v>
       </c>
-      <c r="K100" s="4"/>
-      <c r="L100" s="4"/>
+      <c r="K100" s="4">
+        <v>36</v>
+      </c>
+      <c r="L100" s="4">
+        <v>10</v>
+      </c>
       <c r="M100" s="4">
         <v>37</v>
       </c>
@@ -4787,7 +5182,7 @@
         <v>3099</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C101" s="3">
         <v>35</v>
@@ -4813,8 +5208,12 @@
       <c r="J101" s="4">
         <v>10</v>
       </c>
-      <c r="K101" s="4"/>
-      <c r="L101" s="4"/>
+      <c r="K101" s="4">
+        <v>35</v>
+      </c>
+      <c r="L101" s="4">
+        <v>10</v>
+      </c>
       <c r="M101" s="4">
         <v>29</v>
       </c>
@@ -4827,7 +5226,7 @@
         <v>3100</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C102" s="3">
         <v>29</v>
@@ -4853,8 +5252,12 @@
       <c r="J102" s="4">
         <v>9</v>
       </c>
-      <c r="K102" s="4"/>
-      <c r="L102" s="4"/>
+      <c r="K102" s="4">
+        <v>37</v>
+      </c>
+      <c r="L102" s="4">
+        <v>6</v>
+      </c>
       <c r="M102" s="4">
         <v>25</v>
       </c>
@@ -4867,7 +5270,7 @@
         <v>3101</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C103" s="3">
         <v>38</v>
@@ -4893,8 +5296,12 @@
       <c r="J103" s="4">
         <v>10</v>
       </c>
-      <c r="K103" s="4"/>
-      <c r="L103" s="4"/>
+      <c r="K103" s="4">
+        <v>39</v>
+      </c>
+      <c r="L103" s="4">
+        <v>9</v>
+      </c>
       <c r="M103" s="4">
         <v>36</v>
       </c>
@@ -4907,7 +5314,7 @@
         <v>3102</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C104" s="3">
         <v>38</v>
@@ -4933,8 +5340,12 @@
       <c r="J104" s="4">
         <v>10</v>
       </c>
-      <c r="K104" s="4"/>
-      <c r="L104" s="4"/>
+      <c r="K104" s="4">
+        <v>37</v>
+      </c>
+      <c r="L104" s="4">
+        <v>10</v>
+      </c>
       <c r="M104" s="4">
         <v>34</v>
       </c>
@@ -5183,5 +5594,6 @@
     <mergeCell ref="M1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="40" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/m3.xlsx
+++ b/m3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\سعيات\م2 - ف2\steam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C568C73-0BCC-4C00-A48E-B864A48B5455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61880EAA-AF7D-40B5-95E6-FD951C821FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -264,9 +264,6 @@
     <t>كرار حيدر عبود هادي</t>
   </si>
   <si>
-    <t>كوثر حسن نعمة البطاط</t>
-  </si>
-  <si>
     <t>محمد المهدي عيسى لطيف يونس</t>
   </si>
   <si>
@@ -370,6 +367,9 @@
   </si>
   <si>
     <t>منتظر يوسف حميد كاظم</t>
+  </si>
+  <si>
+    <t>كوثر حسن نعمه عيسى</t>
   </si>
 </sst>
 </file>
@@ -801,23 +801,23 @@
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F1" s="8"/>
       <c r="G1" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J1" s="8"/>
       <c r="K1" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L1" s="8"/>
       <c r="M1" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N1" s="8"/>
       <c r="O1" s="7"/>
@@ -2278,7 +2278,7 @@
         <v>3033</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C35" s="3">
         <v>38</v>
@@ -4038,7 +4038,7 @@
         <v>3073</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="C75" s="3">
         <v>32</v>
@@ -4082,7 +4082,7 @@
         <v>3074</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C76" s="3">
         <v>14</v>
@@ -4126,7 +4126,7 @@
         <v>3075</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C77" s="3">
         <v>35</v>
@@ -4170,7 +4170,7 @@
         <v>3076</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C78" s="3">
         <v>29</v>
@@ -4214,7 +4214,7 @@
         <v>3077</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C79" s="3">
         <v>23</v>
@@ -4258,7 +4258,7 @@
         <v>3078</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C80" s="3">
         <v>14</v>
@@ -4302,7 +4302,7 @@
         <v>3079</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C81" s="3">
         <v>26</v>
@@ -4346,7 +4346,7 @@
         <v>3080</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C82" s="3">
         <v>26</v>
@@ -4390,7 +4390,7 @@
         <v>3081</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C83" s="3">
         <v>32</v>
@@ -4434,7 +4434,7 @@
         <v>3082</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C84" s="3">
         <v>14</v>
@@ -4478,7 +4478,7 @@
         <v>3083</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C85" s="3">
         <v>32</v>
@@ -4522,7 +4522,7 @@
         <v>3084</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C86" s="3">
         <v>32</v>
@@ -4566,7 +4566,7 @@
         <v>3085</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C87" s="3">
         <v>29</v>
@@ -4610,7 +4610,7 @@
         <v>3086</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C88" s="3">
         <v>23</v>
@@ -4654,7 +4654,7 @@
         <v>3087</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C89" s="3">
         <v>26</v>
@@ -4698,7 +4698,7 @@
         <v>3088</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C90" s="3">
         <v>26</v>
@@ -4742,7 +4742,7 @@
         <v>3089</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C91" s="3">
         <v>32</v>
@@ -4786,7 +4786,7 @@
         <v>3090</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C92" s="3">
         <v>23</v>
@@ -4830,7 +4830,7 @@
         <v>3091</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C93" s="3">
         <v>23</v>
@@ -4874,7 +4874,7 @@
         <v>3092</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C94" s="3">
         <v>14</v>
@@ -4918,7 +4918,7 @@
         <v>3093</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C95" s="3">
         <v>29</v>
@@ -4962,7 +4962,7 @@
         <v>3094</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C96" s="3">
         <v>32</v>
@@ -5006,7 +5006,7 @@
         <v>3095</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C97" s="3">
         <v>32</v>
@@ -5050,7 +5050,7 @@
         <v>3096</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C98" s="3">
         <v>29</v>
@@ -5094,7 +5094,7 @@
         <v>3097</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C99" s="3">
         <v>32</v>
@@ -5138,7 +5138,7 @@
         <v>3098</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C100" s="3">
         <v>29</v>
@@ -5182,7 +5182,7 @@
         <v>3099</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C101" s="3">
         <v>35</v>
@@ -5226,7 +5226,7 @@
         <v>3100</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C102" s="3">
         <v>29</v>
@@ -5270,7 +5270,7 @@
         <v>3101</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C103" s="3">
         <v>38</v>
@@ -5314,7 +5314,7 @@
         <v>3102</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C104" s="3">
         <v>38</v>

--- a/m3.xlsx
+++ b/m3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\سعيات\م2 - ف2\steam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61880EAA-AF7D-40B5-95E6-FD951C821FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FD7AF5-B317-4724-8A6B-7591E3096367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -324,9 +324,6 @@
     <t>مينا عبد الستار حماد عبد الله</t>
   </si>
   <si>
-    <t>مينا محمد رحيم الركابي</t>
-  </si>
-  <si>
     <t>نبأ غازي عبد الامير حسن</t>
   </si>
   <si>
@@ -370,6 +367,9 @@
   </si>
   <si>
     <t>كوثر حسن نعمه عيسى</t>
+  </si>
+  <si>
+    <t>مينا محمد رحيم مبارك</t>
   </si>
 </sst>
 </file>
@@ -801,23 +801,23 @@
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F1" s="8"/>
       <c r="G1" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J1" s="8"/>
       <c r="K1" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L1" s="8"/>
       <c r="M1" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N1" s="8"/>
       <c r="O1" s="7"/>
@@ -2278,7 +2278,7 @@
         <v>3033</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C35" s="3">
         <v>38</v>
@@ -4038,7 +4038,7 @@
         <v>3073</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C75" s="3">
         <v>32</v>
@@ -4830,7 +4830,7 @@
         <v>3091</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C93" s="3">
         <v>23</v>
@@ -5006,7 +5006,7 @@
         <v>3095</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="C97" s="3">
         <v>32</v>
@@ -5050,7 +5050,7 @@
         <v>3096</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C98" s="3">
         <v>29</v>
@@ -5094,7 +5094,7 @@
         <v>3097</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C99" s="3">
         <v>32</v>
@@ -5138,7 +5138,7 @@
         <v>3098</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C100" s="3">
         <v>29</v>
@@ -5182,7 +5182,7 @@
         <v>3099</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C101" s="3">
         <v>35</v>
@@ -5226,7 +5226,7 @@
         <v>3100</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C102" s="3">
         <v>29</v>
@@ -5270,7 +5270,7 @@
         <v>3101</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C103" s="3">
         <v>38</v>
@@ -5314,7 +5314,7 @@
         <v>3102</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C104" s="3">
         <v>38</v>
